--- a/research/traditional_assets/database/data/germany/germany_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_chemical_basic.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08500419409238885</v>
+        <v>0.08478068151011167</v>
       </c>
       <c r="C2">
-        <v>404.49383063246</v>
+        <v>401.5209992284747</v>
       </c>
       <c r="D2">
-        <v>334.59383063246</v>
+        <v>335.9289992284747</v>
       </c>
       <c r="E2">
-        <v>-82.90000000000001</v>
+        <v>-78.59200000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.308</v>
       </c>
       <c r="G2">
         <v>69.90000000000001</v>
@@ -1579,28 +1579,28 @@
         <v>44.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2166924</v>
       </c>
       <c r="N2">
-        <v>44.2</v>
+        <v>43.9833076</v>
       </c>
       <c r="O2">
-        <v>13.26</v>
+        <v>13.19499228</v>
       </c>
       <c r="P2">
-        <v>30.94</v>
+        <v>30.78831532</v>
       </c>
       <c r="Q2">
-        <v>56.44</v>
+        <v>56.28831532</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08500419409238885</v>
+        <v>0.08528139546475927</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470865</v>
+        <v>0.9118105188166113</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>203.9757739542319</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08478068151011167</v>
+        <v>0.08455716892783451</v>
       </c>
       <c r="C3">
-        <v>401.5209992284747</v>
+        <v>398.5588662721689</v>
       </c>
       <c r="D3">
-        <v>335.9289992284747</v>
+        <v>337.2748662721688</v>
       </c>
       <c r="E3">
-        <v>-78.59200000000001</v>
+        <v>-74.28400000000001</v>
       </c>
       <c r="F3">
-        <v>4.308</v>
+        <v>8.616</v>
       </c>
       <c r="G3">
         <v>69.90000000000001</v>
@@ -1661,28 +1661,28 @@
         <v>44.2</v>
       </c>
       <c r="M3">
-        <v>0.2166924</v>
+        <v>0.4333848</v>
       </c>
       <c r="N3">
-        <v>43.9833076</v>
+        <v>43.7666152</v>
       </c>
       <c r="O3">
-        <v>13.19499228</v>
+        <v>13.12998456</v>
       </c>
       <c r="P3">
-        <v>30.78831532</v>
+        <v>30.63663064</v>
       </c>
       <c r="Q3">
-        <v>56.28831532</v>
+        <v>56.13663064000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08528139546475927</v>
+        <v>0.08556425400799439</v>
       </c>
       <c r="T3">
-        <v>0.9118105188166113</v>
+        <v>0.9183430486834734</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>203.9757739542319</v>
+        <v>101.987886977116</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08455716892783451</v>
+        <v>0.08433365634555734</v>
       </c>
       <c r="C4">
-        <v>398.5588662721689</v>
+        <v>395.6075608676734</v>
       </c>
       <c r="D4">
-        <v>337.2748662721688</v>
+        <v>338.6315608676734</v>
       </c>
       <c r="E4">
-        <v>-74.28400000000001</v>
+        <v>-69.97600000000001</v>
       </c>
       <c r="F4">
-        <v>8.616</v>
+        <v>12.924</v>
       </c>
       <c r="G4">
         <v>69.90000000000001</v>
@@ -1743,28 +1743,28 @@
         <v>44.2</v>
       </c>
       <c r="M4">
-        <v>0.4333848</v>
+        <v>0.6500771999999998</v>
       </c>
       <c r="N4">
-        <v>43.7666152</v>
+        <v>43.5499228</v>
       </c>
       <c r="O4">
-        <v>13.12998456</v>
+        <v>13.06497684</v>
       </c>
       <c r="P4">
-        <v>30.63663064</v>
+        <v>30.48494596</v>
       </c>
       <c r="Q4">
-        <v>56.13663064000001</v>
+        <v>55.98494596</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08556425400799439</v>
+        <v>0.08585294468614159</v>
       </c>
       <c r="T4">
-        <v>0.9183430486834734</v>
+        <v>0.9250102698877966</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.987886977116</v>
+        <v>67.99192465141066</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08433365634555734</v>
+        <v>0.08411014376328017</v>
       </c>
       <c r="C5">
-        <v>395.6075608676734</v>
+        <v>392.6672142048042</v>
       </c>
       <c r="D5">
-        <v>338.6315608676734</v>
+        <v>339.9992142048041</v>
       </c>
       <c r="E5">
-        <v>-69.97600000000001</v>
+        <v>-65.66800000000001</v>
       </c>
       <c r="F5">
-        <v>12.924</v>
+        <v>17.232</v>
       </c>
       <c r="G5">
         <v>69.90000000000001</v>
@@ -1825,28 +1825,28 @@
         <v>44.2</v>
       </c>
       <c r="M5">
-        <v>0.6500771999999998</v>
+        <v>0.8667695999999999</v>
       </c>
       <c r="N5">
-        <v>43.5499228</v>
+        <v>43.33323040000001</v>
       </c>
       <c r="O5">
-        <v>13.06497684</v>
+        <v>12.99996912</v>
       </c>
       <c r="P5">
-        <v>30.48494596</v>
+        <v>30.33326128</v>
       </c>
       <c r="Q5">
-        <v>55.98494596</v>
+        <v>55.83326128</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08585294468614159</v>
+        <v>0.08614764975341685</v>
       </c>
       <c r="T5">
-        <v>0.9250102698877966</v>
+        <v>0.9318163915338764</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.99192465141066</v>
+        <v>50.99394348855798</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08411014376328017</v>
+        <v>0.08388663118100299</v>
       </c>
       <c r="C6">
-        <v>392.6672142048042</v>
+        <v>389.7379596013507</v>
       </c>
       <c r="D6">
-        <v>339.9992142048041</v>
+        <v>341.3779596013507</v>
       </c>
       <c r="E6">
-        <v>-65.66800000000001</v>
+        <v>-61.36000000000001</v>
       </c>
       <c r="F6">
-        <v>17.232</v>
+        <v>21.54</v>
       </c>
       <c r="G6">
         <v>69.90000000000001</v>
@@ -1907,28 +1907,28 @@
         <v>44.2</v>
       </c>
       <c r="M6">
-        <v>0.8667695999999999</v>
+        <v>1.083462</v>
       </c>
       <c r="N6">
-        <v>43.33323040000001</v>
+        <v>43.11653800000001</v>
       </c>
       <c r="O6">
-        <v>12.99996912</v>
+        <v>12.9349614</v>
       </c>
       <c r="P6">
-        <v>30.33326128</v>
+        <v>30.18157660000001</v>
       </c>
       <c r="Q6">
-        <v>55.83326128</v>
+        <v>55.68157660000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08614764975341685</v>
+        <v>0.0864485591378979</v>
       </c>
       <c r="T6">
-        <v>0.9318163915338764</v>
+        <v>0.9387657999514527</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.99394348855798</v>
+        <v>40.79515479084639</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08388663118100299</v>
+        <v>0.08366311859872584</v>
       </c>
       <c r="C7">
-        <v>389.7379596013507</v>
+        <v>386.8199325463982</v>
       </c>
       <c r="D7">
-        <v>341.3779596013507</v>
+        <v>342.7679325463982</v>
       </c>
       <c r="E7">
-        <v>-61.36000000000001</v>
+        <v>-57.05200000000001</v>
       </c>
       <c r="F7">
-        <v>21.54</v>
+        <v>25.848</v>
       </c>
       <c r="G7">
         <v>69.90000000000001</v>
@@ -1989,28 +1989,28 @@
         <v>44.2</v>
       </c>
       <c r="M7">
-        <v>1.083462</v>
+        <v>1.3001544</v>
       </c>
       <c r="N7">
-        <v>43.11653800000001</v>
+        <v>42.89984560000001</v>
       </c>
       <c r="O7">
-        <v>12.9349614</v>
+        <v>12.86995368</v>
       </c>
       <c r="P7">
-        <v>30.18157660000001</v>
+        <v>30.02989192</v>
       </c>
       <c r="Q7">
-        <v>55.68157660000001</v>
+        <v>55.52989192</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0864485591378979</v>
+        <v>0.08675587084970834</v>
       </c>
       <c r="T7">
-        <v>0.9387657999514527</v>
+        <v>0.9458630681225946</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.79515479084639</v>
+        <v>33.99596232570533</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08366311859872584</v>
+        <v>0.08343960601644869</v>
       </c>
       <c r="C8">
-        <v>386.8199325463982</v>
+        <v>383.9132707447122</v>
       </c>
       <c r="D8">
-        <v>342.7679325463982</v>
+        <v>344.1692707447122</v>
       </c>
       <c r="E8">
-        <v>-57.05200000000001</v>
+        <v>-52.74400000000001</v>
       </c>
       <c r="F8">
-        <v>25.848</v>
+        <v>30.156</v>
       </c>
       <c r="G8">
         <v>69.90000000000001</v>
@@ -2071,28 +2071,28 @@
         <v>44.2</v>
       </c>
       <c r="M8">
-        <v>1.3001544</v>
+        <v>1.5168468</v>
       </c>
       <c r="N8">
-        <v>42.89984560000001</v>
+        <v>42.68315320000001</v>
       </c>
       <c r="O8">
-        <v>12.86995368</v>
+        <v>12.80494596</v>
       </c>
       <c r="P8">
-        <v>30.02989192</v>
+        <v>29.87820724000001</v>
       </c>
       <c r="Q8">
-        <v>55.52989192</v>
+        <v>55.37820724000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08675587084970834</v>
+        <v>0.08706979141553622</v>
       </c>
       <c r="T8">
-        <v>0.9458630681225946</v>
+        <v>0.9531129657167717</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.99596232570533</v>
+        <v>29.13939627917599</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08343960601644869</v>
+        <v>0.08321609343417151</v>
       </c>
       <c r="C9">
-        <v>383.9132707447122</v>
+        <v>381.0181141622164</v>
       </c>
       <c r="D9">
-        <v>344.1692707447122</v>
+        <v>345.5821141622164</v>
       </c>
       <c r="E9">
-        <v>-52.74400000000001</v>
+        <v>-48.43600000000001</v>
       </c>
       <c r="F9">
-        <v>30.156</v>
+        <v>34.464</v>
       </c>
       <c r="G9">
         <v>69.90000000000001</v>
@@ -2153,28 +2153,28 @@
         <v>44.2</v>
       </c>
       <c r="M9">
-        <v>1.5168468</v>
+        <v>1.7335392</v>
       </c>
       <c r="N9">
-        <v>42.6831532</v>
+        <v>42.4664608</v>
       </c>
       <c r="O9">
-        <v>12.80494596</v>
+        <v>12.73993824</v>
       </c>
       <c r="P9">
-        <v>29.87820724</v>
+        <v>29.72652256</v>
       </c>
       <c r="Q9">
-        <v>55.37820724</v>
+        <v>55.22652256</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08706979141553622</v>
+        <v>0.08739053634149077</v>
       </c>
       <c r="T9">
-        <v>0.9531129657167717</v>
+        <v>0.9605204697803875</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.13939627917599</v>
+        <v>25.49697174427899</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08321609343417151</v>
+        <v>0.08299258085189434</v>
       </c>
       <c r="C10">
-        <v>381.0181141622164</v>
+        <v>378.1346050725944</v>
       </c>
       <c r="D10">
-        <v>345.5821141622164</v>
+        <v>347.0066050725944</v>
       </c>
       <c r="E10">
-        <v>-48.43600000000001</v>
+        <v>-44.12800000000001</v>
       </c>
       <c r="F10">
-        <v>34.464</v>
+        <v>38.77199999999999</v>
       </c>
       <c r="G10">
         <v>69.90000000000001</v>
@@ -2235,28 +2235,28 @@
         <v>44.2</v>
       </c>
       <c r="M10">
-        <v>1.7335392</v>
+        <v>1.9502316</v>
       </c>
       <c r="N10">
-        <v>42.4664608</v>
+        <v>42.2497684</v>
       </c>
       <c r="O10">
-        <v>12.73993824</v>
+        <v>12.67493052</v>
       </c>
       <c r="P10">
-        <v>29.72652256</v>
+        <v>29.57483788</v>
       </c>
       <c r="Q10">
-        <v>55.22652256</v>
+        <v>55.07483788</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08739053634149077</v>
+        <v>0.0877183306064773</v>
       </c>
       <c r="T10">
-        <v>0.9605204697803875</v>
+        <v>0.9680907761311155</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.49697174427899</v>
+        <v>22.66397488380355</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08299258085189434</v>
+        <v>0.08276906826961716</v>
       </c>
       <c r="C11">
-        <v>378.1346050725944</v>
+        <v>375.2628881050505</v>
       </c>
       <c r="D11">
-        <v>347.0066050725944</v>
+        <v>348.4428881050505</v>
       </c>
       <c r="E11">
-        <v>-44.12800000000001</v>
+        <v>-39.82000000000001</v>
       </c>
       <c r="F11">
-        <v>38.77199999999999</v>
+        <v>43.07999999999999</v>
       </c>
       <c r="G11">
         <v>69.90000000000001</v>
@@ -2317,28 +2317,28 @@
         <v>44.2</v>
       </c>
       <c r="M11">
-        <v>1.9502316</v>
+        <v>2.166923999999999</v>
       </c>
       <c r="N11">
-        <v>42.2497684</v>
+        <v>42.033076</v>
       </c>
       <c r="O11">
-        <v>12.67493052</v>
+        <v>12.6099228</v>
       </c>
       <c r="P11">
-        <v>29.57483788</v>
+        <v>29.4231532</v>
       </c>
       <c r="Q11">
-        <v>55.07483788</v>
+        <v>54.9231532</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0877183306064773</v>
+        <v>0.08805340918846352</v>
       </c>
       <c r="T11">
-        <v>0.9680907761311155</v>
+        <v>0.9758293115118598</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.66397488380355</v>
+        <v>20.39757739542319</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08276906826961716</v>
+        <v>0.08254555568734001</v>
       </c>
       <c r="C12">
-        <v>375.2628881050505</v>
+        <v>372.40311029326</v>
       </c>
       <c r="D12">
-        <v>348.4428881050505</v>
+        <v>349.89111029326</v>
       </c>
       <c r="E12">
-        <v>-39.82000000000001</v>
+        <v>-35.51200000000001</v>
       </c>
       <c r="F12">
-        <v>43.08</v>
+        <v>47.388</v>
       </c>
       <c r="G12">
         <v>69.90000000000001</v>
@@ -2399,28 +2399,28 @@
         <v>44.2</v>
       </c>
       <c r="M12">
-        <v>2.166924</v>
+        <v>2.3836164</v>
       </c>
       <c r="N12">
-        <v>42.033076</v>
+        <v>41.8163836</v>
       </c>
       <c r="O12">
-        <v>12.6099228</v>
+        <v>12.54491508</v>
       </c>
       <c r="P12">
-        <v>29.4231532</v>
+        <v>29.27146852</v>
       </c>
       <c r="Q12">
-        <v>54.9231532</v>
+        <v>54.77146852</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08805340918846352</v>
+        <v>0.08839601762622473</v>
       </c>
       <c r="T12">
-        <v>0.9758293115118598</v>
+        <v>0.9837417465640816</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.39757739542319</v>
+        <v>18.54325217765745</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08254555568734001</v>
+        <v>0.08232204310506284</v>
       </c>
       <c r="C13">
-        <v>372.40311029326</v>
+        <v>369.5554211255466</v>
       </c>
       <c r="D13">
-        <v>349.89111029326</v>
+        <v>351.3514211255466</v>
       </c>
       <c r="E13">
-        <v>-35.51200000000001</v>
+        <v>-31.20400000000001</v>
       </c>
       <c r="F13">
-        <v>47.388</v>
+        <v>51.69599999999999</v>
       </c>
       <c r="G13">
         <v>69.90000000000001</v>
@@ -2481,28 +2481,28 @@
         <v>44.2</v>
       </c>
       <c r="M13">
-        <v>2.3836164</v>
+        <v>2.600308799999999</v>
       </c>
       <c r="N13">
-        <v>41.8163836</v>
+        <v>41.5996912</v>
       </c>
       <c r="O13">
-        <v>12.54491508</v>
+        <v>12.47990736</v>
       </c>
       <c r="P13">
-        <v>29.27146852</v>
+        <v>29.11978384</v>
       </c>
       <c r="Q13">
-        <v>54.77146852</v>
+        <v>54.61978384</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08839601762622473</v>
+        <v>0.08874641261938959</v>
       </c>
       <c r="T13">
-        <v>0.9837417465640816</v>
+        <v>0.991834009685672</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.54325217765745</v>
+        <v>16.99798116285266</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08232204310506284</v>
+        <v>0.08209853052278569</v>
       </c>
       <c r="C14">
-        <v>369.5554211255466</v>
+        <v>366.7199725963195</v>
       </c>
       <c r="D14">
-        <v>351.3514211255466</v>
+        <v>352.8239725963195</v>
       </c>
       <c r="E14">
-        <v>-31.20400000000001</v>
+        <v>-26.89600000000001</v>
       </c>
       <c r="F14">
-        <v>51.69599999999999</v>
+        <v>56.004</v>
       </c>
       <c r="G14">
         <v>69.90000000000001</v>
@@ -2563,28 +2563,28 @@
         <v>44.2</v>
       </c>
       <c r="M14">
-        <v>2.600308799999999</v>
+        <v>2.8170012</v>
       </c>
       <c r="N14">
-        <v>41.5996912</v>
+        <v>41.3829988</v>
       </c>
       <c r="O14">
-        <v>12.47990736</v>
+        <v>12.41489964</v>
       </c>
       <c r="P14">
-        <v>29.11978384</v>
+        <v>28.96809916</v>
       </c>
       <c r="Q14">
-        <v>54.61978384</v>
+        <v>54.46809916</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08874641261938959</v>
+        <v>0.0891048626698686</v>
       </c>
       <c r="T14">
-        <v>0.991834009685672</v>
+        <v>1.00011230184454</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.99798116285266</v>
+        <v>15.69044415032553</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08209853052278569</v>
+        <v>0.08187501794050851</v>
       </c>
       <c r="C15">
-        <v>366.7199725963195</v>
+        <v>363.8969192588127</v>
       </c>
       <c r="D15">
-        <v>352.8239725963195</v>
+        <v>354.3089192588127</v>
       </c>
       <c r="E15">
-        <v>-26.89600000000001</v>
+        <v>-22.58800000000001</v>
       </c>
       <c r="F15">
-        <v>56.004</v>
+        <v>60.312</v>
       </c>
       <c r="G15">
         <v>69.90000000000001</v>
@@ -2645,28 +2645,28 @@
         <v>44.2</v>
       </c>
       <c r="M15">
-        <v>2.8170012</v>
+        <v>3.0336936</v>
       </c>
       <c r="N15">
-        <v>41.3829988</v>
+        <v>41.1663064</v>
       </c>
       <c r="O15">
-        <v>12.41489964</v>
+        <v>12.34989192</v>
       </c>
       <c r="P15">
-        <v>28.96809916</v>
+        <v>28.81641448</v>
       </c>
       <c r="Q15">
-        <v>54.46809916</v>
+        <v>54.31641448000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0891048626698686</v>
+        <v>0.08947164876803315</v>
       </c>
       <c r="T15">
-        <v>1.00011230184454</v>
+        <v>1.008583112425708</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.69044415032553</v>
+        <v>14.569698139588</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08187501794050851</v>
+        <v>0.08165150535823135</v>
       </c>
       <c r="C16">
-        <v>363.8969192588127</v>
+        <v>361.0864182791578</v>
       </c>
       <c r="D16">
-        <v>354.3089192588127</v>
+        <v>355.8064182791578</v>
       </c>
       <c r="E16">
-        <v>-22.58800000000001</v>
+        <v>-18.28</v>
       </c>
       <c r="F16">
-        <v>60.312</v>
+        <v>64.62</v>
       </c>
       <c r="G16">
         <v>69.90000000000001</v>
@@ -2727,28 +2727,28 @@
         <v>44.2</v>
       </c>
       <c r="M16">
-        <v>3.0336936</v>
+        <v>3.250386</v>
       </c>
       <c r="N16">
-        <v>41.1663064</v>
+        <v>40.949614</v>
       </c>
       <c r="O16">
-        <v>12.34989192</v>
+        <v>12.2848842</v>
       </c>
       <c r="P16">
-        <v>28.81641448</v>
+        <v>28.6647298</v>
       </c>
       <c r="Q16">
-        <v>54.31641448000001</v>
+        <v>54.1647298</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08947164876803315</v>
+        <v>0.089847065127331</v>
       </c>
       <c r="T16">
-        <v>1.008583112425708</v>
+        <v>1.017253236197021</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.569698139588</v>
+        <v>13.59838493028213</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08165150535823135</v>
+        <v>0.08159599277595417</v>
       </c>
       <c r="C17">
-        <v>361.0864182791578</v>
+        <v>357.1523082543537</v>
       </c>
       <c r="D17">
-        <v>355.8064182791578</v>
+        <v>356.1803082543537</v>
       </c>
       <c r="E17">
-        <v>-18.28000000000002</v>
+        <v>-13.97200000000001</v>
       </c>
       <c r="F17">
-        <v>64.61999999999999</v>
+        <v>68.928</v>
       </c>
       <c r="G17">
         <v>69.90000000000001</v>
@@ -2809,45 +2809,45 @@
         <v>44.2</v>
       </c>
       <c r="M17">
-        <v>3.250385999999999</v>
+        <v>3.5704704</v>
       </c>
       <c r="N17">
-        <v>40.949614</v>
+        <v>40.62952960000001</v>
       </c>
       <c r="O17">
-        <v>12.2848842</v>
+        <v>12.18885888</v>
       </c>
       <c r="P17">
-        <v>28.6647298</v>
+        <v>28.44067072</v>
       </c>
       <c r="Q17">
-        <v>54.1647298</v>
+        <v>53.94067072</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.089847065127331</v>
+        <v>0.09023141997137402</v>
       </c>
       <c r="T17">
-        <v>1.017253236197021</v>
+        <v>1.026129791486698</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.59838493028213</v>
+        <v>12.37932122333237</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08159599277595417</v>
+        <v>0.08138298019367701</v>
       </c>
       <c r="C18">
-        <v>357.1523082543537</v>
+        <v>354.2863189623024</v>
       </c>
       <c r="D18">
-        <v>356.1803082543537</v>
+        <v>357.6223189623024</v>
       </c>
       <c r="E18">
-        <v>-13.97200000000001</v>
+        <v>-9.664000000000001</v>
       </c>
       <c r="F18">
-        <v>68.928</v>
+        <v>73.236</v>
       </c>
       <c r="G18">
         <v>69.90000000000001</v>
@@ -2891,28 +2891,28 @@
         <v>44.2</v>
       </c>
       <c r="M18">
-        <v>3.5704704</v>
+        <v>3.7936248</v>
       </c>
       <c r="N18">
-        <v>40.62952960000001</v>
+        <v>40.4063752</v>
       </c>
       <c r="O18">
-        <v>12.18885888</v>
+        <v>12.12191256</v>
       </c>
       <c r="P18">
-        <v>28.44067072</v>
+        <v>28.28446264</v>
       </c>
       <c r="Q18">
-        <v>53.94067072</v>
+        <v>53.78446264</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09023141997137402</v>
+        <v>0.09062503637792413</v>
       </c>
       <c r="T18">
-        <v>1.026129791486698</v>
+        <v>1.035220239674922</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.37932122333237</v>
+        <v>11.65112585725399</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08138298019367701</v>
+        <v>0.08116996761139983</v>
       </c>
       <c r="C19">
-        <v>354.2863189623024</v>
+        <v>351.4320532134728</v>
       </c>
       <c r="D19">
-        <v>357.6223189623024</v>
+        <v>359.0760532134728</v>
       </c>
       <c r="E19">
-        <v>-9.664000000000001</v>
+        <v>-5.356000000000009</v>
       </c>
       <c r="F19">
-        <v>73.236</v>
+        <v>77.544</v>
       </c>
       <c r="G19">
         <v>69.90000000000001</v>
@@ -2973,28 +2973,28 @@
         <v>44.2</v>
       </c>
       <c r="M19">
-        <v>3.7936248</v>
+        <v>4.016779199999999</v>
       </c>
       <c r="N19">
-        <v>40.4063752</v>
+        <v>40.1832208</v>
       </c>
       <c r="O19">
-        <v>12.12191256</v>
+        <v>12.05496624</v>
       </c>
       <c r="P19">
-        <v>28.28446264</v>
+        <v>28.12825456</v>
       </c>
       <c r="Q19">
-        <v>53.78446264</v>
+        <v>53.62825456</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09062503637792413</v>
+        <v>0.09102825318463395</v>
       </c>
       <c r="T19">
-        <v>1.035220239674922</v>
+        <v>1.044532406111639</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.65112585725399</v>
+        <v>11.00384108740655</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08116996761139984</v>
+        <v>0.08095695502912269</v>
       </c>
       <c r="C20">
-        <v>351.4320532134728</v>
+        <v>348.5896545599668</v>
       </c>
       <c r="D20">
-        <v>359.0760532134728</v>
+        <v>360.5416545599668</v>
       </c>
       <c r="E20">
-        <v>-5.356000000000023</v>
+        <v>-1.048000000000016</v>
       </c>
       <c r="F20">
-        <v>77.54399999999998</v>
+        <v>81.85199999999999</v>
       </c>
       <c r="G20">
         <v>69.90000000000001</v>
@@ -3055,28 +3055,28 @@
         <v>44.2</v>
       </c>
       <c r="M20">
-        <v>4.016779199999999</v>
+        <v>4.2399336</v>
       </c>
       <c r="N20">
-        <v>40.1832208</v>
+        <v>39.9600664</v>
       </c>
       <c r="O20">
-        <v>12.05496624</v>
+        <v>11.98801992</v>
       </c>
       <c r="P20">
-        <v>28.12825456</v>
+        <v>27.97204648</v>
       </c>
       <c r="Q20">
-        <v>53.62825456</v>
+        <v>53.47204648</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09102825318463395</v>
+        <v>0.09144142596187985</v>
       </c>
       <c r="T20">
-        <v>1.044532406111639</v>
+        <v>1.05407450258383</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.00384108740655</v>
+        <v>10.42469155649041</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08095695502912269</v>
+        <v>0.08074394244684552</v>
       </c>
       <c r="C21">
-        <v>348.5896545599668</v>
+        <v>345.7592689071752</v>
       </c>
       <c r="D21">
-        <v>360.5416545599668</v>
+        <v>362.0192689071751</v>
       </c>
       <c r="E21">
-        <v>-1.048000000000016</v>
+        <v>3.259999999999991</v>
       </c>
       <c r="F21">
-        <v>81.85199999999999</v>
+        <v>86.16</v>
       </c>
       <c r="G21">
         <v>69.90000000000001</v>
@@ -3137,28 +3137,28 @@
         <v>44.2</v>
       </c>
       <c r="M21">
-        <v>4.2399336</v>
+        <v>4.463088</v>
       </c>
       <c r="N21">
-        <v>39.9600664</v>
+        <v>39.736912</v>
       </c>
       <c r="O21">
-        <v>11.98801992</v>
+        <v>11.9210736</v>
       </c>
       <c r="P21">
-        <v>27.97204648</v>
+        <v>27.8158384</v>
       </c>
       <c r="Q21">
-        <v>53.47204648</v>
+        <v>53.3158384</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09144142596187985</v>
+        <v>0.09186492805855689</v>
       </c>
       <c r="T21">
-        <v>1.05407450258383</v>
+        <v>1.063855151467827</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.42469155649041</v>
+        <v>9.903456978665893</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08074394244684552</v>
+        <v>0.08078082986456836</v>
       </c>
       <c r="C22">
-        <v>345.7592689071752</v>
+        <v>341.194523771997</v>
       </c>
       <c r="D22">
-        <v>362.0192689071751</v>
+        <v>361.7625237719971</v>
       </c>
       <c r="E22">
-        <v>3.259999999999991</v>
+        <v>7.567999999999998</v>
       </c>
       <c r="F22">
-        <v>86.16</v>
+        <v>90.468</v>
       </c>
       <c r="G22">
         <v>69.90000000000001</v>
@@ -3219,45 +3219,45 @@
         <v>44.2</v>
       </c>
       <c r="M22">
-        <v>4.463088</v>
+        <v>4.840038</v>
       </c>
       <c r="N22">
-        <v>39.736912</v>
+        <v>39.359962</v>
       </c>
       <c r="O22">
-        <v>11.9210736</v>
+        <v>11.8079886</v>
       </c>
       <c r="P22">
-        <v>27.8158384</v>
+        <v>27.5519734</v>
       </c>
       <c r="Q22">
-        <v>53.3158384</v>
+        <v>53.0519734</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09186492805855689</v>
+        <v>0.09229915172730171</v>
       </c>
       <c r="T22">
-        <v>1.063855151467827</v>
+        <v>1.073883411715975</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.903456978665893</v>
+        <v>9.132159706184126</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08078082986456833</v>
+        <v>0.08057971728229119</v>
       </c>
       <c r="C23">
-        <v>341.1945237719973</v>
+        <v>338.2907517005253</v>
       </c>
       <c r="D23">
-        <v>361.7625237719973</v>
+        <v>363.1667517005253</v>
       </c>
       <c r="E23">
-        <v>7.567999999999984</v>
+        <v>11.87599999999999</v>
       </c>
       <c r="F23">
-        <v>90.46799999999999</v>
+        <v>94.776</v>
       </c>
       <c r="G23">
         <v>69.90000000000001</v>
@@ -3301,28 +3301,28 @@
         <v>44.2</v>
       </c>
       <c r="M23">
-        <v>4.840037999999999</v>
+        <v>5.070516</v>
       </c>
       <c r="N23">
-        <v>39.359962</v>
+        <v>39.12948400000001</v>
       </c>
       <c r="O23">
-        <v>11.8079886</v>
+        <v>11.7388452</v>
       </c>
       <c r="P23">
-        <v>27.5519734</v>
+        <v>27.3906388</v>
       </c>
       <c r="Q23">
-        <v>53.0519734</v>
+        <v>52.8906388</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09229915172730169</v>
+        <v>0.09274450933627075</v>
       </c>
       <c r="T23">
-        <v>1.073883411715975</v>
+        <v>1.084168806842281</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.132159706184128</v>
+        <v>8.717061537721211</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08057971728229119</v>
+        <v>0.080378604700014</v>
       </c>
       <c r="C24">
-        <v>338.2907517005253</v>
+        <v>335.3979234929691</v>
       </c>
       <c r="D24">
-        <v>363.1667517005253</v>
+        <v>364.5819234929692</v>
       </c>
       <c r="E24">
-        <v>11.87599999999999</v>
+        <v>16.18399999999998</v>
       </c>
       <c r="F24">
-        <v>94.776</v>
+        <v>99.08399999999999</v>
       </c>
       <c r="G24">
         <v>69.90000000000001</v>
@@ -3383,28 +3383,28 @@
         <v>44.2</v>
       </c>
       <c r="M24">
-        <v>5.070516</v>
+        <v>5.300993999999999</v>
       </c>
       <c r="N24">
-        <v>39.12948400000001</v>
+        <v>38.899006</v>
       </c>
       <c r="O24">
-        <v>11.7388452</v>
+        <v>11.6697018</v>
       </c>
       <c r="P24">
-        <v>27.3906388</v>
+        <v>27.2293042</v>
       </c>
       <c r="Q24">
-        <v>52.8906388</v>
+        <v>52.7293042</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09274450933627075</v>
+        <v>0.09320143467534286</v>
       </c>
       <c r="T24">
-        <v>1.084168806842281</v>
+        <v>1.09472135508875</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.717061537721211</v>
+        <v>8.338058862168115</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.080378604700014</v>
+        <v>0.08017749211773685</v>
       </c>
       <c r="C25">
-        <v>335.3979234929691</v>
+        <v>332.5161675864799</v>
       </c>
       <c r="D25">
-        <v>364.5819234929692</v>
+        <v>366.0081675864798</v>
       </c>
       <c r="E25">
-        <v>16.18399999999998</v>
+        <v>20.49199999999999</v>
       </c>
       <c r="F25">
-        <v>99.08399999999999</v>
+        <v>103.392</v>
       </c>
       <c r="G25">
         <v>69.90000000000001</v>
@@ -3465,28 +3465,28 @@
         <v>44.2</v>
       </c>
       <c r="M25">
-        <v>5.300993999999999</v>
+        <v>5.531472</v>
       </c>
       <c r="N25">
-        <v>38.899006</v>
+        <v>38.668528</v>
       </c>
       <c r="O25">
-        <v>11.6697018</v>
+        <v>11.6005584</v>
       </c>
       <c r="P25">
-        <v>27.2293042</v>
+        <v>27.0679696</v>
       </c>
       <c r="Q25">
-        <v>52.7293042</v>
+        <v>52.5679696</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09320143467534286</v>
+        <v>0.09367038436544323</v>
       </c>
       <c r="T25">
-        <v>1.09472135508875</v>
+        <v>1.105551601973285</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.338058862168115</v>
+        <v>7.99063974291111</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08017749211773685</v>
+        <v>0.07997637953545969</v>
       </c>
       <c r="C26">
-        <v>332.5161675864799</v>
+        <v>329.6456144358866</v>
       </c>
       <c r="D26">
-        <v>366.0081675864798</v>
+        <v>367.4456144358865</v>
       </c>
       <c r="E26">
-        <v>20.49199999999998</v>
+        <v>24.79999999999998</v>
       </c>
       <c r="F26">
-        <v>103.392</v>
+        <v>107.7</v>
       </c>
       <c r="G26">
         <v>69.90000000000001</v>
@@ -3547,28 +3547,28 @@
         <v>44.2</v>
       </c>
       <c r="M26">
-        <v>5.531471999999999</v>
+        <v>5.76195</v>
       </c>
       <c r="N26">
-        <v>38.668528</v>
+        <v>38.43805</v>
       </c>
       <c r="O26">
-        <v>11.6005584</v>
+        <v>11.531415</v>
       </c>
       <c r="P26">
-        <v>27.0679696</v>
+        <v>26.906635</v>
       </c>
       <c r="Q26">
-        <v>52.5679696</v>
+        <v>52.406635</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09367038436544323</v>
+        <v>0.09415183938061292</v>
       </c>
       <c r="T26">
-        <v>1.105551601973285</v>
+        <v>1.116670655441407</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.990639742911111</v>
+        <v>7.671014153194666</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07997637953545969</v>
+        <v>0.07992086695318251</v>
       </c>
       <c r="C27">
-        <v>329.6456144358866</v>
+        <v>325.73637970941</v>
       </c>
       <c r="D27">
-        <v>367.4456144358865</v>
+        <v>367.8443797094099</v>
       </c>
       <c r="E27">
-        <v>24.79999999999998</v>
+        <v>29.10799999999999</v>
       </c>
       <c r="F27">
-        <v>107.7</v>
+        <v>112.008</v>
       </c>
       <c r="G27">
         <v>69.90000000000001</v>
@@ -3629,45 +3629,45 @@
         <v>44.2</v>
       </c>
       <c r="M27">
-        <v>5.76195</v>
+        <v>6.0820344</v>
       </c>
       <c r="N27">
-        <v>38.43805</v>
+        <v>38.11796560000001</v>
       </c>
       <c r="O27">
-        <v>11.531415</v>
+        <v>11.43538968</v>
       </c>
       <c r="P27">
-        <v>26.906635</v>
+        <v>26.68257592</v>
       </c>
       <c r="Q27">
-        <v>52.406635</v>
+        <v>52.18257592</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09415183938061292</v>
+        <v>0.09464630669348989</v>
       </c>
       <c r="T27">
-        <v>1.116670655441407</v>
+        <v>1.128090223868127</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.671014153194666</v>
+        <v>7.267305163548567</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07992086695318251</v>
+        <v>0.07972535437090535</v>
       </c>
       <c r="C28">
-        <v>325.73637970941</v>
+        <v>322.8397299042138</v>
       </c>
       <c r="D28">
-        <v>367.8443797094099</v>
+        <v>369.2557299042138</v>
       </c>
       <c r="E28">
-        <v>29.10799999999999</v>
+        <v>33.41599999999998</v>
       </c>
       <c r="F28">
-        <v>112.008</v>
+        <v>116.316</v>
       </c>
       <c r="G28">
         <v>69.90000000000001</v>
@@ -3711,28 +3711,28 @@
         <v>44.2</v>
       </c>
       <c r="M28">
-        <v>6.0820344</v>
+        <v>6.3159588</v>
       </c>
       <c r="N28">
-        <v>38.11796560000001</v>
+        <v>37.88404120000001</v>
       </c>
       <c r="O28">
-        <v>11.43538968</v>
+        <v>11.36521236</v>
       </c>
       <c r="P28">
-        <v>26.68257592</v>
+        <v>26.51882884</v>
       </c>
       <c r="Q28">
-        <v>52.18257592</v>
+        <v>52.01882884</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09464630669348989</v>
+        <v>0.09515432105603473</v>
       </c>
       <c r="T28">
-        <v>1.128090223868127</v>
+        <v>1.13982265718325</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.267305163548567</v>
+        <v>6.998145713046767</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07972535437090535</v>
+        <v>0.07952984178862817</v>
       </c>
       <c r="C29">
-        <v>322.8397299042138</v>
+        <v>319.9539519867129</v>
       </c>
       <c r="D29">
-        <v>369.2557299042138</v>
+        <v>370.677951986713</v>
       </c>
       <c r="E29">
-        <v>33.41599999999998</v>
+        <v>37.72399999999999</v>
       </c>
       <c r="F29">
-        <v>116.316</v>
+        <v>120.624</v>
       </c>
       <c r="G29">
         <v>69.90000000000001</v>
@@ -3793,28 +3793,28 @@
         <v>44.2</v>
       </c>
       <c r="M29">
-        <v>6.3159588</v>
+        <v>6.5498832</v>
       </c>
       <c r="N29">
-        <v>37.88404120000001</v>
+        <v>37.65011680000001</v>
       </c>
       <c r="O29">
-        <v>11.36521236</v>
+        <v>11.29503504</v>
       </c>
       <c r="P29">
-        <v>26.51882884</v>
+        <v>26.35508176</v>
       </c>
       <c r="Q29">
-        <v>52.01882884</v>
+        <v>51.85508176</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09515432105603473</v>
+        <v>0.09567644692865024</v>
       </c>
       <c r="T29">
-        <v>1.13982265718325</v>
+        <v>1.151880991423793</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.998145713046767</v>
+        <v>6.748211937580812</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07952984178862817</v>
+        <v>0.07933432920635101</v>
       </c>
       <c r="C30">
-        <v>319.9539519867129</v>
+        <v>317.0791720648211</v>
       </c>
       <c r="D30">
-        <v>370.677951986713</v>
+        <v>372.1111720648211</v>
       </c>
       <c r="E30">
-        <v>37.72399999999999</v>
+        <v>42.032</v>
       </c>
       <c r="F30">
-        <v>120.624</v>
+        <v>124.932</v>
       </c>
       <c r="G30">
         <v>69.90000000000001</v>
@@ -3875,28 +3875,28 @@
         <v>44.2</v>
       </c>
       <c r="M30">
-        <v>6.5498832</v>
+        <v>6.7838076</v>
       </c>
       <c r="N30">
-        <v>37.65011680000001</v>
+        <v>37.4161924</v>
       </c>
       <c r="O30">
-        <v>11.29503504</v>
+        <v>11.22485772</v>
       </c>
       <c r="P30">
-        <v>26.35508176</v>
+        <v>26.19133468</v>
       </c>
       <c r="Q30">
-        <v>51.85508176</v>
+        <v>51.69133468</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09567644692865024</v>
+        <v>0.09621328057232538</v>
       </c>
       <c r="T30">
-        <v>1.151880991423793</v>
+        <v>1.164278997051394</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.748211937580812</v>
+        <v>6.515514974215955</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07933432920635101</v>
+        <v>0.07913881662407383</v>
       </c>
       <c r="C31">
-        <v>317.0791720648212</v>
+        <v>314.2155182043991</v>
       </c>
       <c r="D31">
-        <v>372.1111720648211</v>
+        <v>373.5555182043991</v>
       </c>
       <c r="E31">
-        <v>42.03199999999997</v>
+        <v>46.33999999999997</v>
       </c>
       <c r="F31">
-        <v>124.932</v>
+        <v>129.24</v>
       </c>
       <c r="G31">
         <v>69.90000000000001</v>
@@ -3957,28 +3957,28 @@
         <v>44.2</v>
       </c>
       <c r="M31">
-        <v>6.783807599999998</v>
+        <v>7.017731999999999</v>
       </c>
       <c r="N31">
-        <v>37.41619240000001</v>
+        <v>37.18226800000001</v>
       </c>
       <c r="O31">
-        <v>11.22485772</v>
+        <v>11.1546804</v>
       </c>
       <c r="P31">
-        <v>26.19133468</v>
+        <v>26.0275876</v>
       </c>
       <c r="Q31">
-        <v>51.69133468</v>
+        <v>51.5275876</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09621328057232538</v>
+        <v>0.0967654523201055</v>
       </c>
       <c r="T31">
-        <v>1.164278997051394</v>
+        <v>1.177031231411213</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.515514974215957</v>
+        <v>6.298331141742092</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07913881662407383</v>
+        <v>0.07916030404179668</v>
       </c>
       <c r="C32">
-        <v>314.2155182043991</v>
+        <v>309.7482320520106</v>
       </c>
       <c r="D32">
-        <v>373.5555182043991</v>
+        <v>373.3962320520106</v>
       </c>
       <c r="E32">
-        <v>46.33999999999997</v>
+        <v>50.64799999999997</v>
       </c>
       <c r="F32">
-        <v>129.24</v>
+        <v>133.548</v>
       </c>
       <c r="G32">
         <v>69.90000000000001</v>
@@ -4039,45 +4039,45 @@
         <v>44.2</v>
       </c>
       <c r="M32">
-        <v>7.017731999999999</v>
+        <v>7.385204399999999</v>
       </c>
       <c r="N32">
-        <v>37.18226800000001</v>
+        <v>36.8147956</v>
       </c>
       <c r="O32">
-        <v>11.1546804</v>
+        <v>11.04443868</v>
       </c>
       <c r="P32">
-        <v>26.0275876</v>
+        <v>25.77035692</v>
       </c>
       <c r="Q32">
-        <v>51.5275876</v>
+        <v>51.27035692</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0967654523201055</v>
+        <v>0.09733362904608214</v>
       </c>
       <c r="T32">
-        <v>1.177031231411213</v>
+        <v>1.190153095752474</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.298331141742092</v>
+        <v>5.984939292946314</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07916030404179668</v>
+        <v>0.07897179145951951</v>
       </c>
       <c r="C33">
-        <v>309.7482320520106</v>
+        <v>306.8423244093581</v>
       </c>
       <c r="D33">
-        <v>373.3962320520106</v>
+        <v>374.7983244093581</v>
       </c>
       <c r="E33">
-        <v>50.64799999999997</v>
+        <v>54.95599999999999</v>
       </c>
       <c r="F33">
-        <v>133.548</v>
+        <v>137.856</v>
       </c>
       <c r="G33">
         <v>69.90000000000001</v>
@@ -4121,28 +4121,28 @@
         <v>44.2</v>
       </c>
       <c r="M33">
-        <v>7.385204399999999</v>
+        <v>7.6234368</v>
       </c>
       <c r="N33">
-        <v>36.8147956</v>
+        <v>36.5765632</v>
       </c>
       <c r="O33">
-        <v>11.04443868</v>
+        <v>10.97296896</v>
       </c>
       <c r="P33">
-        <v>25.77035692</v>
+        <v>25.60359424</v>
       </c>
       <c r="Q33">
-        <v>51.27035692</v>
+        <v>51.10359424</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09733362904608214</v>
+        <v>0.09791851685223457</v>
       </c>
       <c r="T33">
-        <v>1.190153095752474</v>
+        <v>1.203660897280244</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.984939292946314</v>
+        <v>5.797909940041741</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07897179145951951</v>
+        <v>0.07878327887724235</v>
       </c>
       <c r="C34">
-        <v>306.8423244093581</v>
+        <v>303.946986089008</v>
       </c>
       <c r="D34">
-        <v>374.7983244093581</v>
+        <v>376.210986089008</v>
       </c>
       <c r="E34">
-        <v>54.95599999999999</v>
+        <v>59.26399999999998</v>
       </c>
       <c r="F34">
-        <v>137.856</v>
+        <v>142.164</v>
       </c>
       <c r="G34">
         <v>69.90000000000001</v>
@@ -4203,28 +4203,28 @@
         <v>44.2</v>
       </c>
       <c r="M34">
-        <v>7.6234368</v>
+        <v>7.8616692</v>
       </c>
       <c r="N34">
-        <v>36.5765632</v>
+        <v>36.3383308</v>
       </c>
       <c r="O34">
-        <v>10.97296896</v>
+        <v>10.90149924</v>
       </c>
       <c r="P34">
-        <v>25.60359424</v>
+        <v>25.43683156</v>
       </c>
       <c r="Q34">
-        <v>51.10359424</v>
+        <v>50.93683156</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09791851685223457</v>
+        <v>0.09852086399588411</v>
       </c>
       <c r="T34">
-        <v>1.203660897280244</v>
+        <v>1.217571916764067</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.797909940041741</v>
+        <v>5.622215699434416</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07878327887724235</v>
+        <v>0.07859476629496517</v>
       </c>
       <c r="C35">
-        <v>303.946986089008</v>
+        <v>301.0623370544038</v>
       </c>
       <c r="D35">
-        <v>376.210986089008</v>
+        <v>377.6343370544037</v>
       </c>
       <c r="E35">
-        <v>59.26399999999998</v>
+        <v>63.572</v>
       </c>
       <c r="F35">
-        <v>142.164</v>
+        <v>146.472</v>
       </c>
       <c r="G35">
         <v>69.90000000000001</v>
@@ -4285,28 +4285,28 @@
         <v>44.2</v>
       </c>
       <c r="M35">
-        <v>7.8616692</v>
+        <v>8.099901600000001</v>
       </c>
       <c r="N35">
-        <v>36.3383308</v>
+        <v>36.1000984</v>
       </c>
       <c r="O35">
-        <v>10.90149924</v>
+        <v>10.83002952</v>
       </c>
       <c r="P35">
-        <v>25.43683156</v>
+        <v>25.27006888</v>
       </c>
       <c r="Q35">
-        <v>50.93683156</v>
+        <v>50.77006888</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09852086399588411</v>
+        <v>0.09914146408328058</v>
       </c>
       <c r="T35">
-        <v>1.217571916764067</v>
+        <v>1.231904482292854</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.622215699434416</v>
+        <v>5.456856414156932</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07859476629496517</v>
+        <v>0.07840625371268801</v>
       </c>
       <c r="C36">
-        <v>301.0623370544038</v>
+        <v>298.1884990913547</v>
       </c>
       <c r="D36">
-        <v>377.6343370544037</v>
+        <v>379.0684990913547</v>
       </c>
       <c r="E36">
-        <v>63.572</v>
+        <v>67.88</v>
       </c>
       <c r="F36">
-        <v>146.472</v>
+        <v>150.78</v>
       </c>
       <c r="G36">
         <v>69.90000000000001</v>
@@ -4367,28 +4367,28 @@
         <v>44.2</v>
       </c>
       <c r="M36">
-        <v>8.099901600000001</v>
+        <v>8.338134</v>
       </c>
       <c r="N36">
-        <v>36.1000984</v>
+        <v>35.86186600000001</v>
       </c>
       <c r="O36">
-        <v>10.83002952</v>
+        <v>10.7585598</v>
       </c>
       <c r="P36">
-        <v>25.27006888</v>
+        <v>25.10330620000001</v>
       </c>
       <c r="Q36">
-        <v>50.77006888</v>
+        <v>50.60330620000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09914146408328058</v>
+        <v>0.09978115955798156</v>
       </c>
       <c r="T36">
-        <v>1.231904482292854</v>
+        <v>1.246678049837911</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.456856414156932</v>
+        <v>5.300946230895306</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07840625371268801</v>
+        <v>0.07821774113041084</v>
       </c>
       <c r="C37">
-        <v>298.1884990913547</v>
+        <v>295.3255958427735</v>
       </c>
       <c r="D37">
-        <v>379.0684990913547</v>
+        <v>380.5135958427735</v>
       </c>
       <c r="E37">
-        <v>67.88</v>
+        <v>72.18799999999999</v>
       </c>
       <c r="F37">
-        <v>150.78</v>
+        <v>155.088</v>
       </c>
       <c r="G37">
         <v>69.90000000000001</v>
@@ -4449,28 +4449,28 @@
         <v>44.2</v>
       </c>
       <c r="M37">
-        <v>8.338134</v>
+        <v>8.5763664</v>
       </c>
       <c r="N37">
-        <v>35.86186600000001</v>
+        <v>35.62363360000001</v>
       </c>
       <c r="O37">
-        <v>10.7585598</v>
+        <v>10.68709008</v>
       </c>
       <c r="P37">
-        <v>25.10330620000001</v>
+        <v>24.93654352</v>
       </c>
       <c r="Q37">
-        <v>50.60330620000001</v>
+        <v>50.43654352</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09978115955798156</v>
+        <v>0.1004408455162669</v>
       </c>
       <c r="T37">
-        <v>1.246678049837911</v>
+        <v>1.261913291368752</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.300946230895306</v>
+        <v>5.153697724481548</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07821774113041086</v>
+        <v>0.07802922854813368</v>
       </c>
       <c r="C38">
-        <v>295.3255958427734</v>
+        <v>292.4737528442085</v>
       </c>
       <c r="D38">
-        <v>380.5135958427733</v>
+        <v>381.9697528442085</v>
       </c>
       <c r="E38">
-        <v>72.18799999999996</v>
+        <v>76.49599999999998</v>
       </c>
       <c r="F38">
-        <v>155.088</v>
+        <v>159.396</v>
       </c>
       <c r="G38">
         <v>69.90000000000001</v>
@@ -4531,28 +4531,28 @@
         <v>44.2</v>
       </c>
       <c r="M38">
-        <v>8.576366399999998</v>
+        <v>8.814598799999999</v>
       </c>
       <c r="N38">
-        <v>35.62363360000001</v>
+        <v>35.3854012</v>
       </c>
       <c r="O38">
-        <v>10.68709008</v>
+        <v>10.61562036</v>
       </c>
       <c r="P38">
-        <v>24.93654352</v>
+        <v>24.76978084</v>
       </c>
       <c r="Q38">
-        <v>50.43654352</v>
+        <v>50.26978084</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1004408455162669</v>
+        <v>0.1011214738859265</v>
       </c>
       <c r="T38">
-        <v>1.261913291368752</v>
+        <v>1.277632191360889</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.153697724481549</v>
+        <v>5.014408596792858</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07802922854813368</v>
+        <v>0.07784071596585651</v>
       </c>
       <c r="C39">
-        <v>292.4737528442085</v>
+        <v>289.6330975601985</v>
       </c>
       <c r="D39">
-        <v>381.9697528442085</v>
+        <v>383.4370975601984</v>
       </c>
       <c r="E39">
-        <v>76.49599999999998</v>
+        <v>80.80399999999997</v>
       </c>
       <c r="F39">
-        <v>159.396</v>
+        <v>163.704</v>
       </c>
       <c r="G39">
         <v>69.90000000000001</v>
@@ -4613,28 +4613,28 @@
         <v>44.2</v>
       </c>
       <c r="M39">
-        <v>8.814598799999999</v>
+        <v>9.0528312</v>
       </c>
       <c r="N39">
-        <v>35.3854012</v>
+        <v>35.1471688</v>
       </c>
       <c r="O39">
-        <v>10.61562036</v>
+        <v>10.54415064</v>
       </c>
       <c r="P39">
-        <v>24.76978084</v>
+        <v>24.60301816</v>
       </c>
       <c r="Q39">
-        <v>50.26978084</v>
+        <v>50.10301816</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1011214738859265</v>
+        <v>0.101824058009446</v>
       </c>
       <c r="T39">
-        <v>1.277632191360889</v>
+        <v>1.293858152643095</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.014408596792858</v>
+        <v>4.882450475824625</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07784071596585651</v>
+        <v>0.07765220338357935</v>
       </c>
       <c r="C40">
-        <v>289.6330975601985</v>
+        <v>286.8037594214655</v>
       </c>
       <c r="D40">
-        <v>383.4370975601984</v>
+        <v>384.9157594214655</v>
       </c>
       <c r="E40">
-        <v>80.80399999999997</v>
+        <v>85.11199999999999</v>
       </c>
       <c r="F40">
-        <v>163.704</v>
+        <v>168.012</v>
       </c>
       <c r="G40">
         <v>69.90000000000001</v>
@@ -4695,28 +4695,28 @@
         <v>44.2</v>
       </c>
       <c r="M40">
-        <v>9.0528312</v>
+        <v>9.291063600000001</v>
       </c>
       <c r="N40">
-        <v>35.1471688</v>
+        <v>34.9089364</v>
       </c>
       <c r="O40">
-        <v>10.54415064</v>
+        <v>10.47268092</v>
       </c>
       <c r="P40">
-        <v>24.60301816</v>
+        <v>24.43625548</v>
       </c>
       <c r="Q40">
-        <v>50.10301816</v>
+        <v>49.93625548</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.101824058009446</v>
+        <v>0.1025496776779989</v>
       </c>
       <c r="T40">
-        <v>1.293858152643095</v>
+        <v>1.310616112655865</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.882450475824625</v>
+        <v>4.757259437982967</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07765220338357935</v>
+        <v>0.07746369080130219</v>
       </c>
       <c r="C41">
-        <v>286.8037594214655</v>
+        <v>283.9858698629736</v>
       </c>
       <c r="D41">
-        <v>384.9157594214655</v>
+        <v>386.4058698629736</v>
       </c>
       <c r="E41">
-        <v>85.11199999999999</v>
+        <v>89.41999999999999</v>
       </c>
       <c r="F41">
-        <v>168.012</v>
+        <v>172.32</v>
       </c>
       <c r="G41">
         <v>69.90000000000001</v>
@@ -4777,28 +4777,28 @@
         <v>44.2</v>
       </c>
       <c r="M41">
-        <v>9.291063600000001</v>
+        <v>9.529296</v>
       </c>
       <c r="N41">
-        <v>34.9089364</v>
+        <v>34.670704</v>
       </c>
       <c r="O41">
-        <v>10.47268092</v>
+        <v>10.4012112</v>
       </c>
       <c r="P41">
-        <v>24.43625548</v>
+        <v>24.2694928</v>
       </c>
       <c r="Q41">
-        <v>49.93625548</v>
+        <v>49.7694928</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1025496776779989</v>
+        <v>0.103299484668837</v>
       </c>
       <c r="T41">
-        <v>1.310616112655865</v>
+        <v>1.327932671335727</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.757259437982967</v>
+        <v>4.638327952033393</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07746369080130219</v>
+        <v>0.07727517821902501</v>
       </c>
       <c r="C42">
-        <v>283.9858698629736</v>
+        <v>281.1795623628749</v>
       </c>
       <c r="D42">
-        <v>386.4058698629736</v>
+        <v>387.907562362875</v>
       </c>
       <c r="E42">
-        <v>89.41999999999999</v>
+        <v>93.72799999999998</v>
       </c>
       <c r="F42">
-        <v>172.32</v>
+        <v>176.628</v>
       </c>
       <c r="G42">
         <v>69.90000000000001</v>
@@ -4859,28 +4859,28 @@
         <v>44.2</v>
       </c>
       <c r="M42">
-        <v>9.529296</v>
+        <v>9.7675284</v>
       </c>
       <c r="N42">
-        <v>34.670704</v>
+        <v>34.4324716</v>
       </c>
       <c r="O42">
-        <v>10.4012112</v>
+        <v>10.32974148</v>
       </c>
       <c r="P42">
-        <v>24.2694928</v>
+        <v>24.10273012</v>
       </c>
       <c r="Q42">
-        <v>49.7694928</v>
+        <v>49.60273012</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.103299484668837</v>
+        <v>0.1040747088458051</v>
       </c>
       <c r="T42">
-        <v>1.327932671335727</v>
+        <v>1.345836232004737</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.638327952033393</v>
+        <v>4.525198001983798</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07727517821902501</v>
+        <v>0.07782166563674785</v>
       </c>
       <c r="C43">
-        <v>281.1795623628749</v>
+        <v>272.5500090050081</v>
       </c>
       <c r="D43">
-        <v>387.907562362875</v>
+        <v>383.5860090050081</v>
       </c>
       <c r="E43">
-        <v>93.72799999999998</v>
+        <v>98.036</v>
       </c>
       <c r="F43">
-        <v>176.628</v>
+        <v>180.936</v>
       </c>
       <c r="G43">
         <v>69.90000000000001</v>
@@ -4941,45 +4941,45 @@
         <v>44.2</v>
       </c>
       <c r="M43">
-        <v>9.7675284</v>
+        <v>10.4581008</v>
       </c>
       <c r="N43">
-        <v>34.4324716</v>
+        <v>33.74189920000001</v>
       </c>
       <c r="O43">
-        <v>10.32974148</v>
+        <v>10.12256976</v>
       </c>
       <c r="P43">
-        <v>24.10273012</v>
+        <v>23.61932944</v>
       </c>
       <c r="Q43">
-        <v>49.60273012</v>
+        <v>49.11932944</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1040747088458051</v>
+        <v>0.1048766648909446</v>
       </c>
       <c r="T43">
-        <v>1.345836232004737</v>
+        <v>1.364357156834748</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.525198001983798</v>
+        <v>4.22638879135684</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07782166563674786</v>
+        <v>0.07765065305447069</v>
       </c>
       <c r="C44">
-        <v>272.550009005008</v>
+        <v>269.5839672316471</v>
       </c>
       <c r="D44">
-        <v>383.586009005008</v>
+        <v>384.9279672316471</v>
       </c>
       <c r="E44">
-        <v>98.03599999999997</v>
+        <v>102.344</v>
       </c>
       <c r="F44">
-        <v>180.936</v>
+        <v>185.244</v>
       </c>
       <c r="G44">
         <v>69.90000000000001</v>
@@ -5023,28 +5023,28 @@
         <v>44.2</v>
       </c>
       <c r="M44">
-        <v>10.4581008</v>
+        <v>10.7071032</v>
       </c>
       <c r="N44">
-        <v>33.74189920000001</v>
+        <v>33.4928968</v>
       </c>
       <c r="O44">
-        <v>10.12256976</v>
+        <v>10.04786904</v>
       </c>
       <c r="P44">
-        <v>23.61932944</v>
+        <v>23.44502776</v>
       </c>
       <c r="Q44">
-        <v>49.11932944</v>
+        <v>48.94502776</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1048766648909446</v>
+        <v>0.1057067597446854</v>
       </c>
       <c r="T44">
-        <v>1.364357156834747</v>
+        <v>1.383527938676337</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.226388791356841</v>
+        <v>4.128100679929937</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07765065305447069</v>
+        <v>0.07747964047219352</v>
       </c>
       <c r="C45">
-        <v>269.5839672316471</v>
+        <v>266.6273479823429</v>
       </c>
       <c r="D45">
-        <v>384.9279672316471</v>
+        <v>386.279347982343</v>
       </c>
       <c r="E45">
-        <v>102.344</v>
+        <v>106.652</v>
       </c>
       <c r="F45">
-        <v>185.244</v>
+        <v>189.552</v>
       </c>
       <c r="G45">
         <v>69.90000000000001</v>
@@ -5105,28 +5105,28 @@
         <v>44.2</v>
       </c>
       <c r="M45">
-        <v>10.7071032</v>
+        <v>10.9561056</v>
       </c>
       <c r="N45">
-        <v>33.4928968</v>
+        <v>33.2438944</v>
       </c>
       <c r="O45">
-        <v>10.04786904</v>
+        <v>9.973168320000001</v>
       </c>
       <c r="P45">
-        <v>23.44502776</v>
+        <v>23.27072608</v>
       </c>
       <c r="Q45">
-        <v>48.94502776</v>
+        <v>48.77072608</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1057067597446854</v>
+        <v>0.1065665008432027</v>
       </c>
       <c r="T45">
-        <v>1.383527938676337</v>
+        <v>1.403383391297984</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.128100679929937</v>
+        <v>4.034280209931529</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07747964047219352</v>
+        <v>0.07841112788991636</v>
       </c>
       <c r="C46">
-        <v>266.6273479823429</v>
+        <v>255.0712802565967</v>
       </c>
       <c r="D46">
-        <v>386.279347982343</v>
+        <v>379.0312802565966</v>
       </c>
       <c r="E46">
-        <v>106.652</v>
+        <v>110.96</v>
       </c>
       <c r="F46">
-        <v>189.552</v>
+        <v>193.86</v>
       </c>
       <c r="G46">
         <v>69.90000000000001</v>
@@ -5187,45 +5187,45 @@
         <v>44.2</v>
       </c>
       <c r="M46">
-        <v>10.9561056</v>
+        <v>11.883618</v>
       </c>
       <c r="N46">
-        <v>33.2438944</v>
+        <v>32.316382</v>
       </c>
       <c r="O46">
-        <v>9.973168320000001</v>
+        <v>9.694914600000001</v>
       </c>
       <c r="P46">
-        <v>23.27072608</v>
+        <v>22.6214674</v>
       </c>
       <c r="Q46">
-        <v>48.77072608</v>
+        <v>48.1214674</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1065665008432027</v>
+        <v>0.1074575052543934</v>
       </c>
       <c r="T46">
-        <v>1.403383391297984</v>
+        <v>1.4239608603786</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.034280209931529</v>
+        <v>3.719405992350142</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07841112788991636</v>
+        <v>0.07826461530763919</v>
       </c>
       <c r="C47">
-        <v>255.0712802565967</v>
+        <v>251.8852402714923</v>
       </c>
       <c r="D47">
-        <v>379.0312802565966</v>
+        <v>380.1532402714923</v>
       </c>
       <c r="E47">
-        <v>110.96</v>
+        <v>115.268</v>
       </c>
       <c r="F47">
-        <v>193.86</v>
+        <v>198.168</v>
       </c>
       <c r="G47">
         <v>69.90000000000001</v>
@@ -5269,28 +5269,28 @@
         <v>44.2</v>
       </c>
       <c r="M47">
-        <v>11.883618</v>
+        <v>12.1476984</v>
       </c>
       <c r="N47">
-        <v>32.316382</v>
+        <v>32.05230160000001</v>
       </c>
       <c r="O47">
-        <v>9.694914600000001</v>
+        <v>9.615690480000001</v>
       </c>
       <c r="P47">
-        <v>22.6214674</v>
+        <v>22.43661112000001</v>
       </c>
       <c r="Q47">
-        <v>48.1214674</v>
+        <v>47.93661112000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1074575052543934</v>
+        <v>0.1083815098289614</v>
       </c>
       <c r="T47">
-        <v>1.4239608603786</v>
+        <v>1.445300457943682</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.719405992350142</v>
+        <v>3.63854934034253</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07826461530763919</v>
+        <v>0.07811810272536202</v>
       </c>
       <c r="C48">
-        <v>251.8852402714923</v>
+        <v>248.7058621717007</v>
       </c>
       <c r="D48">
-        <v>380.1532402714923</v>
+        <v>381.2818621717007</v>
       </c>
       <c r="E48">
-        <v>115.268</v>
+        <v>119.576</v>
       </c>
       <c r="F48">
-        <v>198.168</v>
+        <v>202.476</v>
       </c>
       <c r="G48">
         <v>69.90000000000001</v>
@@ -5351,28 +5351,28 @@
         <v>44.2</v>
       </c>
       <c r="M48">
-        <v>12.1476984</v>
+        <v>12.4117788</v>
       </c>
       <c r="N48">
-        <v>32.05230160000001</v>
+        <v>31.7882212</v>
       </c>
       <c r="O48">
-        <v>9.615690480000001</v>
+        <v>9.53646636</v>
       </c>
       <c r="P48">
-        <v>22.43661112000001</v>
+        <v>22.25175484</v>
       </c>
       <c r="Q48">
-        <v>47.93661112000001</v>
+        <v>47.75175484</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1083815098289614</v>
+        <v>0.109340382500683</v>
       </c>
       <c r="T48">
-        <v>1.445300457943682</v>
+        <v>1.46744532334141</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.63854934034253</v>
+        <v>3.561133396930986</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07811810272536202</v>
+        <v>0.07891239014308485</v>
       </c>
       <c r="C49">
-        <v>248.7058621717007</v>
+        <v>238.358315469212</v>
       </c>
       <c r="D49">
-        <v>381.2818621717007</v>
+        <v>375.242315469212</v>
       </c>
       <c r="E49">
-        <v>119.576</v>
+        <v>123.884</v>
       </c>
       <c r="F49">
-        <v>202.476</v>
+        <v>206.784</v>
       </c>
       <c r="G49">
         <v>69.90000000000001</v>
@@ -5433,45 +5433,45 @@
         <v>44.2</v>
       </c>
       <c r="M49">
-        <v>12.4117788</v>
+        <v>13.2548544</v>
       </c>
       <c r="N49">
-        <v>31.7882212</v>
+        <v>30.9451456</v>
       </c>
       <c r="O49">
-        <v>9.53646636</v>
+        <v>9.283543680000001</v>
       </c>
       <c r="P49">
-        <v>22.25175484</v>
+        <v>21.66160192</v>
       </c>
       <c r="Q49">
-        <v>47.75175484</v>
+        <v>47.16160192</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.109340382500683</v>
+        <v>0.1103361348905478</v>
       </c>
       <c r="T49">
-        <v>1.46744532334141</v>
+        <v>1.490441914331358</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.561133396930986</v>
+        <v>3.334627349810798</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07891239014308485</v>
+        <v>0.07878547756080767</v>
       </c>
       <c r="C50">
-        <v>238.358315469212</v>
+        <v>235.0024483819876</v>
       </c>
       <c r="D50">
-        <v>375.242315469212</v>
+        <v>376.1944483819876</v>
       </c>
       <c r="E50">
-        <v>123.884</v>
+        <v>128.192</v>
       </c>
       <c r="F50">
-        <v>206.784</v>
+        <v>211.092</v>
       </c>
       <c r="G50">
         <v>69.90000000000001</v>
@@ -5515,28 +5515,28 @@
         <v>44.2</v>
       </c>
       <c r="M50">
-        <v>13.2548544</v>
+        <v>13.5309972</v>
       </c>
       <c r="N50">
-        <v>30.9451456</v>
+        <v>30.6690028</v>
       </c>
       <c r="O50">
-        <v>9.283543680000001</v>
+        <v>9.20070084</v>
       </c>
       <c r="P50">
-        <v>21.66160192</v>
+        <v>21.46830196</v>
       </c>
       <c r="Q50">
-        <v>47.16160192</v>
+        <v>46.96830196000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1103361348905478</v>
+        <v>0.1113709363937405</v>
       </c>
       <c r="T50">
-        <v>1.490441914331358</v>
+        <v>1.51434033241895</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.334627349810799</v>
+        <v>3.266573730426904</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07878547756080767</v>
+        <v>0.07865856497853052</v>
       </c>
       <c r="C51">
-        <v>235.0024483819876</v>
+        <v>231.6514254350895</v>
       </c>
       <c r="D51">
-        <v>376.1944483819876</v>
+        <v>377.1514254350895</v>
       </c>
       <c r="E51">
-        <v>128.192</v>
+        <v>132.5</v>
       </c>
       <c r="F51">
-        <v>211.092</v>
+        <v>215.4</v>
       </c>
       <c r="G51">
         <v>69.90000000000001</v>
@@ -5597,28 +5597,28 @@
         <v>44.2</v>
       </c>
       <c r="M51">
-        <v>13.5309972</v>
+        <v>13.80714</v>
       </c>
       <c r="N51">
-        <v>30.6690028</v>
+        <v>30.39286000000001</v>
       </c>
       <c r="O51">
-        <v>9.20070084</v>
+        <v>9.117858000000002</v>
       </c>
       <c r="P51">
-        <v>21.46830196</v>
+        <v>21.275002</v>
       </c>
       <c r="Q51">
-        <v>46.96830196000001</v>
+        <v>46.775002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1113709363937405</v>
+        <v>0.112447129957061</v>
       </c>
       <c r="T51">
-        <v>1.51434033241895</v>
+        <v>1.539194687230047</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.266573730426904</v>
+        <v>3.201242255818367</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07865856497853052</v>
+        <v>0.07853165239625334</v>
       </c>
       <c r="C52">
-        <v>231.6514254350895</v>
+        <v>228.3052836908973</v>
       </c>
       <c r="D52">
-        <v>377.1514254350895</v>
+        <v>378.1132836908973</v>
       </c>
       <c r="E52">
-        <v>132.5</v>
+        <v>136.808</v>
       </c>
       <c r="F52">
-        <v>215.4</v>
+        <v>219.708</v>
       </c>
       <c r="G52">
         <v>69.90000000000001</v>
@@ -5679,28 +5679,28 @@
         <v>44.2</v>
       </c>
       <c r="M52">
-        <v>13.80714</v>
+        <v>14.0832828</v>
       </c>
       <c r="N52">
-        <v>30.39286000000001</v>
+        <v>30.1167172</v>
       </c>
       <c r="O52">
-        <v>9.117858000000002</v>
+        <v>9.03501516</v>
       </c>
       <c r="P52">
-        <v>21.275002</v>
+        <v>21.08170204</v>
       </c>
       <c r="Q52">
-        <v>46.775002</v>
+        <v>46.58170204</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.112447129957061</v>
+        <v>0.1135672497882722</v>
       </c>
       <c r="T52">
-        <v>1.539194687230047</v>
+        <v>1.565063505502821</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.201242255818367</v>
+        <v>3.138472799821928</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07853165239625334</v>
+        <v>0.07840473981397618</v>
       </c>
       <c r="C53">
-        <v>228.3052836908973</v>
+        <v>224.9640605908408</v>
       </c>
       <c r="D53">
-        <v>378.1132836908973</v>
+        <v>379.0800605908408</v>
       </c>
       <c r="E53">
-        <v>136.808</v>
+        <v>141.116</v>
       </c>
       <c r="F53">
-        <v>219.708</v>
+        <v>224.016</v>
       </c>
       <c r="G53">
         <v>69.90000000000001</v>
@@ -5761,28 +5761,28 @@
         <v>44.2</v>
       </c>
       <c r="M53">
-        <v>14.0832828</v>
+        <v>14.3594256</v>
       </c>
       <c r="N53">
-        <v>30.1167172</v>
+        <v>29.8405744</v>
       </c>
       <c r="O53">
-        <v>9.03501516</v>
+        <v>8.952172320000001</v>
       </c>
       <c r="P53">
-        <v>21.08170204</v>
+        <v>20.88840208</v>
       </c>
       <c r="Q53">
-        <v>46.58170204</v>
+        <v>46.38840208</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1135672497882722</v>
+        <v>0.114734041279117</v>
       </c>
       <c r="T53">
-        <v>1.565063505502821</v>
+        <v>1.592010191203627</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.138472799821928</v>
+        <v>3.078117553671506</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07840473981397618</v>
+        <v>0.07827782723169902</v>
       </c>
       <c r="C54">
-        <v>224.9640605908408</v>
+        <v>221.6277939602594</v>
       </c>
       <c r="D54">
-        <v>379.0800605908408</v>
+        <v>380.0517939602594</v>
       </c>
       <c r="E54">
-        <v>141.116</v>
+        <v>145.424</v>
       </c>
       <c r="F54">
-        <v>224.016</v>
+        <v>228.324</v>
       </c>
       <c r="G54">
         <v>69.90000000000001</v>
@@ -5843,28 +5843,28 @@
         <v>44.2</v>
       </c>
       <c r="M54">
-        <v>14.3594256</v>
+        <v>14.6355684</v>
       </c>
       <c r="N54">
-        <v>29.8405744</v>
+        <v>29.5644316</v>
       </c>
       <c r="O54">
-        <v>8.952172320000001</v>
+        <v>8.869329480000001</v>
       </c>
       <c r="P54">
-        <v>20.88840208</v>
+        <v>20.69510212</v>
       </c>
       <c r="Q54">
-        <v>46.38840208</v>
+        <v>46.19510212</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.114734041279117</v>
+        <v>0.1159504834717</v>
       </c>
       <c r="T54">
-        <v>1.592010191203627</v>
+        <v>1.620103544381063</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.078117553671506</v>
+        <v>3.020039863979591</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07827782723169902</v>
+        <v>0.08109931464942184</v>
       </c>
       <c r="C55">
-        <v>221.6277939602594</v>
+        <v>196.8288479769472</v>
       </c>
       <c r="D55">
-        <v>380.0517939602594</v>
+        <v>359.5608479769472</v>
       </c>
       <c r="E55">
-        <v>145.424</v>
+        <v>149.732</v>
       </c>
       <c r="F55">
-        <v>228.324</v>
+        <v>232.632</v>
       </c>
       <c r="G55">
         <v>69.90000000000001</v>
@@ -5925,45 +5925,45 @@
         <v>44.2</v>
       </c>
       <c r="M55">
-        <v>14.6355684</v>
+        <v>16.7262408</v>
       </c>
       <c r="N55">
-        <v>29.5644316</v>
+        <v>27.4737592</v>
       </c>
       <c r="O55">
-        <v>8.869329480000001</v>
+        <v>8.242127760000001</v>
       </c>
       <c r="P55">
-        <v>20.69510212</v>
+        <v>19.23163144</v>
       </c>
       <c r="Q55">
-        <v>46.19510212</v>
+        <v>44.73163144</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1159504834717</v>
+        <v>0.1172198144552649</v>
       </c>
       <c r="T55">
-        <v>1.620103544381063</v>
+        <v>1.649418347696649</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.3</v>
       </c>
       <c r="W55">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.020039863979591</v>
+        <v>2.642554326971067</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08109931464942184</v>
+        <v>0.08102700206714468</v>
       </c>
       <c r="C56">
-        <v>196.8288479769472</v>
+        <v>193.0183878680431</v>
       </c>
       <c r="D56">
-        <v>359.5608479769472</v>
+        <v>360.0583878680432</v>
       </c>
       <c r="E56">
-        <v>149.732</v>
+        <v>154.04</v>
       </c>
       <c r="F56">
-        <v>232.632</v>
+        <v>236.94</v>
       </c>
       <c r="G56">
         <v>69.90000000000001</v>
@@ -6007,28 +6007,28 @@
         <v>44.2</v>
       </c>
       <c r="M56">
-        <v>16.7262408</v>
+        <v>17.035986</v>
       </c>
       <c r="N56">
-        <v>27.4737592</v>
+        <v>27.164014</v>
       </c>
       <c r="O56">
-        <v>8.242127760000001</v>
+        <v>8.1492042</v>
       </c>
       <c r="P56">
-        <v>19.23163144</v>
+        <v>19.0148098</v>
       </c>
       <c r="Q56">
-        <v>44.73163144</v>
+        <v>44.5148098</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1172198144552649</v>
+        <v>0.1185455601492104</v>
       </c>
       <c r="T56">
-        <v>1.649418347696649</v>
+        <v>1.680036031159594</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.642554326971067</v>
+        <v>2.594507884662502</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08102700206714468</v>
+        <v>0.08095468948486753</v>
       </c>
       <c r="C57">
-        <v>193.0183878680431</v>
+        <v>189.2093066020207</v>
       </c>
       <c r="D57">
-        <v>360.0583878680432</v>
+        <v>360.5573066020207</v>
       </c>
       <c r="E57">
-        <v>154.04</v>
+        <v>158.348</v>
       </c>
       <c r="F57">
-        <v>236.94</v>
+        <v>241.248</v>
       </c>
       <c r="G57">
         <v>69.90000000000001</v>
@@ -6089,28 +6089,28 @@
         <v>44.2</v>
       </c>
       <c r="M57">
-        <v>17.035986</v>
+        <v>17.3457312</v>
       </c>
       <c r="N57">
-        <v>27.164014</v>
+        <v>26.8542688</v>
       </c>
       <c r="O57">
-        <v>8.1492042</v>
+        <v>8.056280640000001</v>
       </c>
       <c r="P57">
-        <v>19.0148098</v>
+        <v>18.79798816</v>
       </c>
       <c r="Q57">
-        <v>44.5148098</v>
+        <v>44.29798816</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1185455601492104</v>
+        <v>0.1199315670110626</v>
       </c>
       <c r="T57">
-        <v>1.680036031159594</v>
+        <v>1.712045427507218</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.594507884662502</v>
+        <v>2.5481773867221</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08095468948486753</v>
+        <v>0.08088237690259034</v>
       </c>
       <c r="C58">
-        <v>189.2093066020207</v>
+        <v>185.4016099186587</v>
       </c>
       <c r="D58">
-        <v>360.5573066020207</v>
+        <v>361.0576099186587</v>
       </c>
       <c r="E58">
-        <v>158.348</v>
+        <v>162.656</v>
       </c>
       <c r="F58">
-        <v>241.248</v>
+        <v>245.556</v>
       </c>
       <c r="G58">
         <v>69.90000000000001</v>
@@ -6171,28 +6171,28 @@
         <v>44.2</v>
       </c>
       <c r="M58">
-        <v>17.3457312</v>
+        <v>17.6554764</v>
       </c>
       <c r="N58">
-        <v>26.8542688</v>
+        <v>26.5445236</v>
       </c>
       <c r="O58">
-        <v>8.056280640000001</v>
+        <v>7.96335708</v>
       </c>
       <c r="P58">
-        <v>18.79798816</v>
+        <v>18.58116652</v>
       </c>
       <c r="Q58">
-        <v>44.29798816</v>
+        <v>44.08116652</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1199315670110626</v>
+        <v>0.1213820393083496</v>
       </c>
       <c r="T58">
-        <v>1.712045427507218</v>
+        <v>1.74554363298729</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.5481773867221</v>
+        <v>2.503472520288379</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08088237690259034</v>
+        <v>0.08239346432031319</v>
       </c>
       <c r="C59">
-        <v>185.4016099186587</v>
+        <v>170.9194699238411</v>
       </c>
       <c r="D59">
-        <v>361.0576099186587</v>
+        <v>350.8834699238412</v>
       </c>
       <c r="E59">
-        <v>162.656</v>
+        <v>166.964</v>
       </c>
       <c r="F59">
-        <v>245.556</v>
+        <v>249.864</v>
       </c>
       <c r="G59">
         <v>69.90000000000001</v>
@@ -6253,45 +6253,45 @@
         <v>44.2</v>
       </c>
       <c r="M59">
-        <v>17.6554764</v>
+        <v>18.9396912</v>
       </c>
       <c r="N59">
-        <v>26.5445236</v>
+        <v>25.2603088</v>
       </c>
       <c r="O59">
-        <v>7.96335708</v>
+        <v>7.578092639999999</v>
       </c>
       <c r="P59">
-        <v>18.58116652</v>
+        <v>17.68221616</v>
       </c>
       <c r="Q59">
-        <v>44.08116652</v>
+        <v>43.18221616</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1213820393083496</v>
+        <v>0.1229015817150314</v>
       </c>
       <c r="T59">
-        <v>1.74554363298729</v>
+        <v>1.78063699110927</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.503472520288379</v>
+        <v>2.333723371371546</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08239346432031318</v>
+        <v>0.08234845173803601</v>
       </c>
       <c r="C60">
-        <v>170.9194699238413</v>
+        <v>166.9062466228563</v>
       </c>
       <c r="D60">
-        <v>350.8834699238413</v>
+        <v>351.1782466228562</v>
       </c>
       <c r="E60">
-        <v>166.9639999999999</v>
+        <v>171.272</v>
       </c>
       <c r="F60">
-        <v>249.8639999999999</v>
+        <v>254.172</v>
       </c>
       <c r="G60">
         <v>69.90000000000001</v>
@@ -6335,28 +6335,28 @@
         <v>44.2</v>
       </c>
       <c r="M60">
-        <v>18.9396912</v>
+        <v>19.2662376</v>
       </c>
       <c r="N60">
-        <v>25.2603088</v>
+        <v>24.9337624</v>
       </c>
       <c r="O60">
-        <v>7.578092640000001</v>
+        <v>7.480128720000001</v>
       </c>
       <c r="P60">
-        <v>17.68221616</v>
+        <v>17.45363368</v>
       </c>
       <c r="Q60">
-        <v>43.18221616</v>
+        <v>42.95363368</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1229015817150314</v>
+        <v>0.1244952481415512</v>
       </c>
       <c r="T60">
-        <v>1.78063699110927</v>
+        <v>1.817442220359151</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.333723371371546</v>
+        <v>2.294168737958469</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08234845173803601</v>
+        <v>0.08230343915575886</v>
       </c>
       <c r="C61">
-        <v>166.9062466228563</v>
+        <v>162.8935190212702</v>
       </c>
       <c r="D61">
-        <v>351.1782466228562</v>
+        <v>351.4735190212701</v>
       </c>
       <c r="E61">
-        <v>171.272</v>
+        <v>175.58</v>
       </c>
       <c r="F61">
-        <v>254.172</v>
+        <v>258.48</v>
       </c>
       <c r="G61">
         <v>69.90000000000001</v>
@@ -6417,28 +6417,28 @@
         <v>44.2</v>
       </c>
       <c r="M61">
-        <v>19.2662376</v>
+        <v>19.592784</v>
       </c>
       <c r="N61">
-        <v>24.9337624</v>
+        <v>24.607216</v>
       </c>
       <c r="O61">
-        <v>7.480128720000001</v>
+        <v>7.382164800000001</v>
       </c>
       <c r="P61">
-        <v>17.45363368</v>
+        <v>17.2250512</v>
       </c>
       <c r="Q61">
-        <v>42.95363368</v>
+        <v>42.7250512</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1244952481415512</v>
+        <v>0.1261685978893971</v>
       </c>
       <c r="T61">
-        <v>1.817442220359151</v>
+        <v>1.856087711071527</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.294168737958469</v>
+        <v>2.255932592325828</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08230343915575886</v>
+        <v>0.08225842657348167</v>
       </c>
       <c r="C62">
-        <v>162.8935190212702</v>
+        <v>158.881288370495</v>
       </c>
       <c r="D62">
-        <v>351.4735190212701</v>
+        <v>351.769288370495</v>
       </c>
       <c r="E62">
-        <v>175.58</v>
+        <v>179.8879999999999</v>
       </c>
       <c r="F62">
-        <v>258.48</v>
+        <v>262.788</v>
       </c>
       <c r="G62">
         <v>69.90000000000001</v>
@@ -6499,28 +6499,28 @@
         <v>44.2</v>
       </c>
       <c r="M62">
-        <v>19.592784</v>
+        <v>19.9193304</v>
       </c>
       <c r="N62">
-        <v>24.607216</v>
+        <v>24.2806696</v>
       </c>
       <c r="O62">
-        <v>7.382164800000001</v>
+        <v>7.28420088</v>
       </c>
       <c r="P62">
-        <v>17.2250512</v>
+        <v>16.99646872</v>
       </c>
       <c r="Q62">
-        <v>42.7250512</v>
+        <v>42.49646872</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1261685978893971</v>
+        <v>0.1279277604448248</v>
       </c>
       <c r="T62">
-        <v>1.856087711071527</v>
+        <v>1.896715021820435</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.255932592325828</v>
+        <v>2.21895009081229</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08225842657348167</v>
+        <v>0.08221341399120452</v>
       </c>
       <c r="C63">
-        <v>158.881288370495</v>
+        <v>154.8695559261581</v>
       </c>
       <c r="D63">
-        <v>351.769288370495</v>
+        <v>352.065555926158</v>
       </c>
       <c r="E63">
-        <v>179.8879999999999</v>
+        <v>184.1959999999999</v>
       </c>
       <c r="F63">
-        <v>262.788</v>
+        <v>267.0959999999999</v>
       </c>
       <c r="G63">
         <v>69.90000000000001</v>
@@ -6581,28 +6581,28 @@
         <v>44.2</v>
       </c>
       <c r="M63">
-        <v>19.9193304</v>
+        <v>20.2458768</v>
       </c>
       <c r="N63">
-        <v>24.2806696</v>
+        <v>23.95412320000001</v>
       </c>
       <c r="O63">
-        <v>7.28420088</v>
+        <v>7.186236960000001</v>
       </c>
       <c r="P63">
-        <v>16.99646872</v>
+        <v>16.76788624</v>
       </c>
       <c r="Q63">
-        <v>42.49646872</v>
+        <v>42.26788624</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1279277604448248</v>
+        <v>0.1297795105031698</v>
       </c>
       <c r="T63">
-        <v>1.896715021820435</v>
+        <v>1.939480612082443</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.21895009081229</v>
+        <v>2.183160573218543</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08221341399120452</v>
+        <v>0.08216840140892737</v>
       </c>
       <c r="C64">
-        <v>154.8695559261581</v>
+        <v>150.8583229481205</v>
       </c>
       <c r="D64">
-        <v>352.065555926158</v>
+        <v>352.3623229481205</v>
       </c>
       <c r="E64">
-        <v>184.1959999999999</v>
+        <v>188.504</v>
       </c>
       <c r="F64">
-        <v>267.0959999999999</v>
+        <v>271.404</v>
       </c>
       <c r="G64">
         <v>69.90000000000001</v>
@@ -6663,28 +6663,28 @@
         <v>44.2</v>
       </c>
       <c r="M64">
-        <v>20.2458768</v>
+        <v>20.5724232</v>
       </c>
       <c r="N64">
-        <v>23.95412320000001</v>
+        <v>23.6275768</v>
       </c>
       <c r="O64">
-        <v>7.186236960000001</v>
+        <v>7.08827304</v>
       </c>
       <c r="P64">
-        <v>16.76788624</v>
+        <v>16.53930376</v>
       </c>
       <c r="Q64">
-        <v>42.26788624</v>
+        <v>42.03930376</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1297795105031698</v>
+        <v>0.1317313551592631</v>
       </c>
       <c r="T64">
-        <v>1.939480612082443</v>
+        <v>1.984557855872128</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.183160573218543</v>
+        <v>2.148507230786502</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08216840140892737</v>
+        <v>0.08212338882665018</v>
       </c>
       <c r="C65">
-        <v>150.8583229481205</v>
+        <v>146.8475907004954</v>
       </c>
       <c r="D65">
-        <v>352.3623229481205</v>
+        <v>352.6595907004954</v>
       </c>
       <c r="E65">
-        <v>188.504</v>
+        <v>192.812</v>
       </c>
       <c r="F65">
-        <v>271.404</v>
+        <v>275.712</v>
       </c>
       <c r="G65">
         <v>69.90000000000001</v>
@@ -6745,28 +6745,28 @@
         <v>44.2</v>
       </c>
       <c r="M65">
-        <v>20.5724232</v>
+        <v>20.8989696</v>
       </c>
       <c r="N65">
-        <v>23.6275768</v>
+        <v>23.3010304</v>
       </c>
       <c r="O65">
-        <v>7.08827304</v>
+        <v>6.99030912</v>
       </c>
       <c r="P65">
-        <v>16.53930376</v>
+        <v>16.31072128</v>
       </c>
       <c r="Q65">
-        <v>42.03930376</v>
+        <v>41.81072128</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1317313551592631</v>
+        <v>0.1337916356295838</v>
       </c>
       <c r="T65">
-        <v>1.984557855872128</v>
+        <v>2.032139390983461</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.148507230786502</v>
+        <v>2.114936805305463</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08212338882665018</v>
+        <v>0.08207837624437303</v>
       </c>
       <c r="C66">
-        <v>146.8475907004954</v>
+        <v>142.8373604516643</v>
       </c>
       <c r="D66">
-        <v>352.6595907004954</v>
+        <v>352.9573604516643</v>
       </c>
       <c r="E66">
-        <v>192.812</v>
+        <v>197.12</v>
       </c>
       <c r="F66">
-        <v>275.712</v>
+        <v>280.02</v>
       </c>
       <c r="G66">
         <v>69.90000000000001</v>
@@ -6827,28 +6827,28 @@
         <v>44.2</v>
       </c>
       <c r="M66">
-        <v>20.8989696</v>
+        <v>21.225516</v>
       </c>
       <c r="N66">
-        <v>23.3010304</v>
+        <v>22.974484</v>
       </c>
       <c r="O66">
-        <v>6.99030912</v>
+        <v>6.892345200000001</v>
       </c>
       <c r="P66">
-        <v>16.31072128</v>
+        <v>16.0821388</v>
       </c>
       <c r="Q66">
-        <v>41.81072128</v>
+        <v>41.5821388</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1337916356295838</v>
+        <v>0.1359696464124943</v>
       </c>
       <c r="T66">
-        <v>2.032139390983461</v>
+        <v>2.082439870958299</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.114936805305463</v>
+        <v>2.082399315993072</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08207837624437303</v>
+        <v>0.08203336366209585</v>
       </c>
       <c r="C67">
-        <v>142.8373604516643</v>
+        <v>138.8276334742973</v>
       </c>
       <c r="D67">
-        <v>352.9573604516643</v>
+        <v>353.2556334742972</v>
       </c>
       <c r="E67">
-        <v>197.12</v>
+        <v>201.428</v>
       </c>
       <c r="F67">
-        <v>280.02</v>
+        <v>284.328</v>
       </c>
       <c r="G67">
         <v>69.90000000000001</v>
@@ -6909,28 +6909,28 @@
         <v>44.2</v>
       </c>
       <c r="M67">
-        <v>21.225516</v>
+        <v>21.5520624</v>
       </c>
       <c r="N67">
-        <v>22.974484</v>
+        <v>22.6479376</v>
       </c>
       <c r="O67">
-        <v>6.892345200000001</v>
+        <v>6.794381280000001</v>
       </c>
       <c r="P67">
-        <v>16.0821388</v>
+        <v>15.85355632</v>
       </c>
       <c r="Q67">
-        <v>41.5821388</v>
+        <v>41.35355632</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1359696464124943</v>
+        <v>0.1382757754767525</v>
       </c>
       <c r="T67">
-        <v>2.082439870958299</v>
+        <v>2.135699202696363</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.082399315993072</v>
+        <v>2.050847811205298</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08203336366209585</v>
+        <v>0.08198835107981869</v>
       </c>
       <c r="C68">
-        <v>138.8276334742973</v>
+        <v>134.818411045369</v>
       </c>
       <c r="D68">
-        <v>353.2556334742972</v>
+        <v>353.5544110453689</v>
       </c>
       <c r="E68">
-        <v>201.428</v>
+        <v>205.736</v>
       </c>
       <c r="F68">
-        <v>284.328</v>
+        <v>288.636</v>
       </c>
       <c r="G68">
         <v>69.90000000000001</v>
@@ -6991,28 +6991,28 @@
         <v>44.2</v>
       </c>
       <c r="M68">
-        <v>21.5520624</v>
+        <v>21.8786088</v>
       </c>
       <c r="N68">
-        <v>22.6479376</v>
+        <v>22.3213912</v>
       </c>
       <c r="O68">
-        <v>6.794381280000001</v>
+        <v>6.696417360000001</v>
       </c>
       <c r="P68">
-        <v>15.85355632</v>
+        <v>15.62497384</v>
       </c>
       <c r="Q68">
-        <v>41.35355632</v>
+        <v>41.12497384</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1382757754767525</v>
+        <v>0.1407216699388445</v>
       </c>
       <c r="T68">
-        <v>2.135699202696363</v>
+        <v>2.192186372721582</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.050847811205298</v>
+        <v>2.020238142381339</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08198835107981869</v>
+        <v>0.08870253849754152</v>
       </c>
       <c r="C69">
-        <v>134.818411045369</v>
+        <v>90.90313690459271</v>
       </c>
       <c r="D69">
-        <v>353.5544110453689</v>
+        <v>313.9471369045927</v>
       </c>
       <c r="E69">
-        <v>205.736</v>
+        <v>210.044</v>
       </c>
       <c r="F69">
-        <v>288.636</v>
+        <v>292.944</v>
       </c>
       <c r="G69">
         <v>69.90000000000001</v>
@@ -7073,45 +7073,45 @@
         <v>44.2</v>
       </c>
       <c r="M69">
-        <v>21.8786088</v>
+        <v>26.36496</v>
       </c>
       <c r="N69">
-        <v>22.3213912</v>
+        <v>17.83504</v>
       </c>
       <c r="O69">
-        <v>6.696417360000001</v>
+        <v>5.350512000000001</v>
       </c>
       <c r="P69">
-        <v>15.62497384</v>
+        <v>12.484528</v>
       </c>
       <c r="Q69">
-        <v>41.12497384</v>
+        <v>37.984528</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1407216699388445</v>
+        <v>0.1433204328048173</v>
       </c>
       <c r="T69">
-        <v>2.192186372721582</v>
+        <v>2.252203990873378</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.020238142381339</v>
+        <v>1.67646755390488</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08870253849754152</v>
+        <v>0.08875692591526435</v>
       </c>
       <c r="C70">
-        <v>90.90313690459271</v>
+        <v>86.31050323107598</v>
       </c>
       <c r="D70">
-        <v>313.9471369045927</v>
+        <v>313.662503231076</v>
       </c>
       <c r="E70">
-        <v>210.044</v>
+        <v>214.352</v>
       </c>
       <c r="F70">
-        <v>292.944</v>
+        <v>297.252</v>
       </c>
       <c r="G70">
         <v>69.90000000000001</v>
@@ -7155,28 +7155,28 @@
         <v>44.2</v>
       </c>
       <c r="M70">
-        <v>26.36496</v>
+        <v>26.75268</v>
       </c>
       <c r="N70">
-        <v>17.83504</v>
+        <v>17.44732</v>
       </c>
       <c r="O70">
-        <v>5.350512000000001</v>
+        <v>5.234196</v>
       </c>
       <c r="P70">
-        <v>12.484528</v>
+        <v>12.213124</v>
       </c>
       <c r="Q70">
-        <v>37.984528</v>
+        <v>37.713124</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1433204328048173</v>
+        <v>0.1460868577911754</v>
       </c>
       <c r="T70">
-        <v>2.252203990873378</v>
+        <v>2.316093713422064</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.67646755390488</v>
+        <v>1.652170922688867</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08875692591526435</v>
+        <v>0.0888113133329872</v>
       </c>
       <c r="C71">
-        <v>86.31050323107598</v>
+        <v>81.71838520451598</v>
       </c>
       <c r="D71">
-        <v>313.662503231076</v>
+        <v>313.378385204516</v>
       </c>
       <c r="E71">
-        <v>214.352</v>
+        <v>218.66</v>
       </c>
       <c r="F71">
-        <v>297.252</v>
+        <v>301.56</v>
       </c>
       <c r="G71">
         <v>69.90000000000001</v>
@@ -7237,28 +7237,28 @@
         <v>44.2</v>
       </c>
       <c r="M71">
-        <v>26.75268</v>
+        <v>27.1404</v>
       </c>
       <c r="N71">
-        <v>17.44732</v>
+        <v>17.0596</v>
       </c>
       <c r="O71">
-        <v>5.234196</v>
+        <v>5.11788</v>
       </c>
       <c r="P71">
-        <v>12.213124</v>
+        <v>11.94172</v>
       </c>
       <c r="Q71">
-        <v>37.713124</v>
+        <v>37.44172</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1460868577911754</v>
+        <v>0.1490377111099573</v>
       </c>
       <c r="T71">
-        <v>2.316093713422064</v>
+        <v>2.384242750807328</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.652170922688867</v>
+        <v>1.628568480936169</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0888113133329872</v>
+        <v>0.08886570075071001</v>
       </c>
       <c r="C72">
-        <v>81.71838520451598</v>
+        <v>77.12678142494934</v>
       </c>
       <c r="D72">
-        <v>313.378385204516</v>
+        <v>313.0947814249493</v>
       </c>
       <c r="E72">
-        <v>218.66</v>
+        <v>222.968</v>
       </c>
       <c r="F72">
-        <v>301.56</v>
+        <v>305.868</v>
       </c>
       <c r="G72">
         <v>69.90000000000001</v>
@@ -7319,28 +7319,28 @@
         <v>44.2</v>
       </c>
       <c r="M72">
-        <v>27.1404</v>
+        <v>27.52812</v>
       </c>
       <c r="N72">
-        <v>17.0596</v>
+        <v>16.67188000000001</v>
       </c>
       <c r="O72">
-        <v>5.11788</v>
+        <v>5.001564000000001</v>
       </c>
       <c r="P72">
-        <v>11.94172</v>
+        <v>11.670316</v>
       </c>
       <c r="Q72">
-        <v>37.44172</v>
+        <v>37.170316</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1490377111099573</v>
+        <v>0.1521920715541725</v>
       </c>
       <c r="T72">
-        <v>2.384242750807328</v>
+        <v>2.45709172180537</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.628568480936169</v>
+        <v>1.605630896697632</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08886570075071001</v>
+        <v>0.08892008816843286</v>
       </c>
       <c r="C73">
-        <v>77.1267814249494</v>
+        <v>72.53569049747568</v>
       </c>
       <c r="D73">
-        <v>313.0947814249493</v>
+        <v>312.8116904974756</v>
       </c>
       <c r="E73">
-        <v>222.9679999999999</v>
+        <v>227.2759999999999</v>
       </c>
       <c r="F73">
-        <v>305.8679999999999</v>
+        <v>310.1759999999999</v>
       </c>
       <c r="G73">
         <v>69.90000000000001</v>
@@ -7401,28 +7401,28 @@
         <v>44.2</v>
       </c>
       <c r="M73">
-        <v>27.52811999999999</v>
+        <v>27.91583999999999</v>
       </c>
       <c r="N73">
-        <v>16.67188000000001</v>
+        <v>16.28416000000001</v>
       </c>
       <c r="O73">
-        <v>5.001564000000003</v>
+        <v>4.885248000000003</v>
       </c>
       <c r="P73">
-        <v>11.67031600000001</v>
+        <v>11.39891200000001</v>
       </c>
       <c r="Q73">
-        <v>37.17031600000001</v>
+        <v>36.89891200000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1521920715541725</v>
+        <v>0.1555717434586888</v>
       </c>
       <c r="T73">
-        <v>2.457091721805369</v>
+        <v>2.535144190731842</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.605630896697632</v>
+        <v>1.583330467576832</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08892008816843286</v>
+        <v>0.08897447558615568</v>
       </c>
       <c r="C74">
-        <v>72.53569049747568</v>
+        <v>67.94511103223527</v>
       </c>
       <c r="D74">
-        <v>312.8116904974756</v>
+        <v>312.5291110322353</v>
       </c>
       <c r="E74">
-        <v>227.2759999999999</v>
+        <v>231.584</v>
       </c>
       <c r="F74">
-        <v>310.1759999999999</v>
+        <v>314.484</v>
       </c>
       <c r="G74">
         <v>69.90000000000001</v>
@@ -7483,28 +7483,28 @@
         <v>44.2</v>
       </c>
       <c r="M74">
-        <v>27.91583999999999</v>
+        <v>28.30356</v>
       </c>
       <c r="N74">
-        <v>16.28416000000001</v>
+        <v>15.89644000000001</v>
       </c>
       <c r="O74">
-        <v>4.885248000000003</v>
+        <v>4.768932000000001</v>
       </c>
       <c r="P74">
-        <v>11.39891200000001</v>
+        <v>11.127508</v>
       </c>
       <c r="Q74">
-        <v>36.89891200000001</v>
+        <v>36.62750800000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1555717434586888</v>
+        <v>0.1592017614302062</v>
       </c>
       <c r="T74">
-        <v>2.535144190731842</v>
+        <v>2.618978324023239</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.583330467576832</v>
+        <v>1.561641009116875</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08897447558615568</v>
+        <v>0.08902886300387852</v>
       </c>
       <c r="C75">
-        <v>67.94511103223527</v>
+        <v>63.35504164438584</v>
       </c>
       <c r="D75">
-        <v>312.5291110322353</v>
+        <v>312.2470416443858</v>
       </c>
       <c r="E75">
-        <v>231.584</v>
+        <v>235.892</v>
       </c>
       <c r="F75">
-        <v>314.484</v>
+        <v>318.792</v>
       </c>
       <c r="G75">
         <v>69.90000000000001</v>
@@ -7565,28 +7565,28 @@
         <v>44.2</v>
       </c>
       <c r="M75">
-        <v>28.30356</v>
+        <v>28.69128</v>
       </c>
       <c r="N75">
-        <v>15.89644000000001</v>
+        <v>15.50872000000001</v>
       </c>
       <c r="O75">
-        <v>4.768932000000001</v>
+        <v>4.652616000000002</v>
       </c>
       <c r="P75">
-        <v>11.127508</v>
+        <v>10.85610400000001</v>
       </c>
       <c r="Q75">
-        <v>36.62750800000001</v>
+        <v>36.356104</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1592017614302062</v>
+        <v>0.1631110115533789</v>
       </c>
       <c r="T75">
-        <v>2.618978324023239</v>
+        <v>2.709261236798589</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.561641009116875</v>
+        <v>1.540537752236917</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08902886300387852</v>
+        <v>0.08908325042160134</v>
       </c>
       <c r="C76">
-        <v>63.35504164438584</v>
+        <v>58.76548095408015</v>
       </c>
       <c r="D76">
-        <v>312.2470416443858</v>
+        <v>311.9654809540801</v>
       </c>
       <c r="E76">
-        <v>235.892</v>
+        <v>240.2</v>
       </c>
       <c r="F76">
-        <v>318.792</v>
+        <v>323.1</v>
       </c>
       <c r="G76">
         <v>69.90000000000001</v>
@@ -7647,28 +7647,28 @@
         <v>44.2</v>
       </c>
       <c r="M76">
-        <v>28.69128</v>
+        <v>29.079</v>
       </c>
       <c r="N76">
-        <v>15.50872000000001</v>
+        <v>15.12100000000001</v>
       </c>
       <c r="O76">
-        <v>4.652616000000002</v>
+        <v>4.536300000000002</v>
       </c>
       <c r="P76">
-        <v>10.85610400000001</v>
+        <v>10.58470000000001</v>
       </c>
       <c r="Q76">
-        <v>36.356104</v>
+        <v>36.08470000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1631110115533789</v>
+        <v>0.1673330016864054</v>
       </c>
       <c r="T76">
-        <v>2.709261236798589</v>
+        <v>2.806766782595968</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.540537752236917</v>
+        <v>1.519997248873758</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08908325042160134</v>
+        <v>0.1227642027312643</v>
       </c>
       <c r="C77">
-        <v>58.76548095408015</v>
+        <v>-57.32715721292726</v>
       </c>
       <c r="D77">
-        <v>311.9654809540801</v>
+        <v>200.1808427870727</v>
       </c>
       <c r="E77">
-        <v>240.2</v>
+        <v>244.508</v>
       </c>
       <c r="F77">
-        <v>323.1</v>
+        <v>327.408</v>
       </c>
       <c r="G77">
         <v>69.90000000000001</v>
@@ -7729,45 +7729,45 @@
         <v>44.2</v>
       </c>
       <c r="M77">
-        <v>29.079</v>
+        <v>48.0634944</v>
       </c>
       <c r="N77">
-        <v>15.12100000000001</v>
+        <v>-3.863494399999993</v>
       </c>
       <c r="O77">
-        <v>4.536300000000002</v>
+        <v>-1.159048319999998</v>
       </c>
       <c r="P77">
-        <v>10.58470000000001</v>
+        <v>-2.704446079999995</v>
       </c>
       <c r="Q77">
-        <v>36.08470000000001</v>
+        <v>22.79555392</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1673330016864054</v>
+        <v>0.1749006125873246</v>
       </c>
       <c r="T77">
-        <v>2.806766782595968</v>
+        <v>2.981538396935902</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.3</v>
+        <v>0.2758850592436325</v>
       </c>
       <c r="W77">
-        <v>0.063</v>
+        <v>0.1063000733030347</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.519997248873758</v>
+        <v>0.9196168641454419</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1227642027312643</v>
+        <v>0.1237742027312643</v>
       </c>
       <c r="C78">
-        <v>-57.32715721292726</v>
+        <v>-63.76326411826977</v>
       </c>
       <c r="D78">
-        <v>200.1808427870727</v>
+        <v>198.0527358817301</v>
       </c>
       <c r="E78">
-        <v>244.508</v>
+        <v>248.8159999999999</v>
       </c>
       <c r="F78">
-        <v>327.408</v>
+        <v>331.716</v>
       </c>
       <c r="G78">
         <v>69.90000000000001</v>
@@ -7811,37 +7811,37 @@
         <v>44.2</v>
       </c>
       <c r="M78">
-        <v>48.0634944</v>
+        <v>48.6959088</v>
       </c>
       <c r="N78">
-        <v>-3.863494399999993</v>
+        <v>-4.495908799999995</v>
       </c>
       <c r="O78">
-        <v>-1.159048319999998</v>
+        <v>-1.348772639999998</v>
       </c>
       <c r="P78">
-        <v>-2.704446079999995</v>
+        <v>-3.147136159999997</v>
       </c>
       <c r="Q78">
-        <v>22.79555392</v>
+        <v>22.35286384</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1749006125873246</v>
+        <v>0.1805136826998169</v>
       </c>
       <c r="T78">
-        <v>2.981538396935902</v>
+        <v>3.111170501150507</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2758850592436325</v>
+        <v>0.2723021363963126</v>
       </c>
       <c r="W78">
-        <v>0.1063000733030347</v>
+        <v>0.1068260463770213</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9196168641454419</v>
+        <v>0.9076737879877088</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1237742027312643</v>
+        <v>0.1247842027312643</v>
       </c>
       <c r="C79">
-        <v>-63.76326411826977</v>
+        <v>-70.1545995094757</v>
       </c>
       <c r="D79">
-        <v>198.0527358817301</v>
+        <v>195.9694004905243</v>
       </c>
       <c r="E79">
-        <v>248.8159999999999</v>
+        <v>253.124</v>
       </c>
       <c r="F79">
-        <v>331.716</v>
+        <v>336.024</v>
       </c>
       <c r="G79">
         <v>69.90000000000001</v>
@@ -7893,37 +7893,37 @@
         <v>44.2</v>
       </c>
       <c r="M79">
-        <v>48.6959088</v>
+        <v>49.32832320000001</v>
       </c>
       <c r="N79">
-        <v>-4.495908799999995</v>
+        <v>-5.128323200000004</v>
       </c>
       <c r="O79">
-        <v>-1.348772639999998</v>
+        <v>-1.538496960000001</v>
       </c>
       <c r="P79">
-        <v>-3.147136159999997</v>
+        <v>-3.589826240000003</v>
       </c>
       <c r="Q79">
-        <v>22.35286384</v>
+        <v>21.91017376</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1805136826998169</v>
+        <v>0.186637031913445</v>
       </c>
       <c r="T79">
-        <v>3.111170501150507</v>
+        <v>3.252587342111894</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2723021363963126</v>
+        <v>0.2688110833655906</v>
       </c>
       <c r="W79">
-        <v>0.1068260463770213</v>
+        <v>0.1073385329619313</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9076737879877088</v>
+        <v>0.8960369445519688</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1247842027312643</v>
+        <v>0.1257942027312643</v>
       </c>
       <c r="C80">
-        <v>-70.1545995094757</v>
+        <v>-76.50256154649662</v>
       </c>
       <c r="D80">
-        <v>195.9694004905243</v>
+        <v>193.9294384535034</v>
       </c>
       <c r="E80">
-        <v>253.124</v>
+        <v>257.432</v>
       </c>
       <c r="F80">
-        <v>336.024</v>
+        <v>340.332</v>
       </c>
       <c r="G80">
         <v>69.90000000000001</v>
@@ -7975,37 +7975,37 @@
         <v>44.2</v>
       </c>
       <c r="M80">
-        <v>49.32832320000001</v>
+        <v>49.9607376</v>
       </c>
       <c r="N80">
-        <v>-5.128323200000004</v>
+        <v>-5.760737599999999</v>
       </c>
       <c r="O80">
-        <v>-1.538496960000001</v>
+        <v>-1.72822128</v>
       </c>
       <c r="P80">
-        <v>-3.589826240000003</v>
+        <v>-4.032516319999999</v>
       </c>
       <c r="Q80">
-        <v>21.91017376</v>
+        <v>21.46748368</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.186637031913445</v>
+        <v>0.1933435572426567</v>
       </c>
       <c r="T80">
-        <v>3.252587342111894</v>
+        <v>3.407472453641032</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2688110833655906</v>
+        <v>0.265408411424254</v>
       </c>
       <c r="W80">
-        <v>0.1073385329619313</v>
+        <v>0.1078380452029195</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8960369445519688</v>
+        <v>0.8846947047475135</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1257942027312643</v>
+        <v>0.1268042027312643</v>
       </c>
       <c r="C81">
-        <v>-76.50256154649662</v>
+        <v>-82.8084907719437</v>
       </c>
       <c r="D81">
-        <v>193.9294384535034</v>
+        <v>191.9315092280563</v>
       </c>
       <c r="E81">
-        <v>257.432</v>
+        <v>261.74</v>
       </c>
       <c r="F81">
-        <v>340.332</v>
+        <v>344.64</v>
       </c>
       <c r="G81">
         <v>69.90000000000001</v>
@@ -8057,37 +8057,37 @@
         <v>44.2</v>
       </c>
       <c r="M81">
-        <v>49.9607376</v>
+        <v>50.593152</v>
       </c>
       <c r="N81">
-        <v>-5.760737599999999</v>
+        <v>-6.393152000000001</v>
       </c>
       <c r="O81">
-        <v>-1.72822128</v>
+        <v>-1.9179456</v>
       </c>
       <c r="P81">
-        <v>-4.032516319999999</v>
+        <v>-4.4752064</v>
       </c>
       <c r="Q81">
-        <v>21.46748368</v>
+        <v>21.0247936</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1933435572426567</v>
+        <v>0.2007207351047895</v>
       </c>
       <c r="T81">
-        <v>3.407472453641032</v>
+        <v>3.577846076323083</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.265408411424254</v>
+        <v>0.2620908062814509</v>
       </c>
       <c r="W81">
-        <v>0.1078380452029195</v>
+        <v>0.108325069637883</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8846947047475135</v>
+        <v>0.8736360209381697</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1268042027312643</v>
+        <v>0.1278142027312643</v>
       </c>
       <c r="C82">
-        <v>-82.8084907719437</v>
+        <v>-89.07367304879267</v>
       </c>
       <c r="D82">
-        <v>191.9315092280563</v>
+        <v>189.9743269512073</v>
       </c>
       <c r="E82">
-        <v>261.74</v>
+        <v>266.048</v>
       </c>
       <c r="F82">
-        <v>344.64</v>
+        <v>348.948</v>
       </c>
       <c r="G82">
         <v>69.90000000000001</v>
@@ -8139,37 +8139,37 @@
         <v>44.2</v>
       </c>
       <c r="M82">
-        <v>50.593152</v>
+        <v>51.22556640000001</v>
       </c>
       <c r="N82">
-        <v>-6.393152000000001</v>
+        <v>-7.025566400000002</v>
       </c>
       <c r="O82">
-        <v>-1.9179456</v>
+        <v>-2.107669920000001</v>
       </c>
       <c r="P82">
-        <v>-4.4752064</v>
+        <v>-4.917896480000001</v>
       </c>
       <c r="Q82">
-        <v>21.0247936</v>
+        <v>20.58210352</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2007207351047895</v>
+        <v>0.2088744580050416</v>
       </c>
       <c r="T82">
-        <v>3.577846076323083</v>
+        <v>3.766153764550614</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2620908062814509</v>
+        <v>0.2588551173150132</v>
       </c>
       <c r="W82">
-        <v>0.108325069637883</v>
+        <v>0.1088000687781561</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8736360209381697</v>
+        <v>0.862850391050044</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1278142027312643</v>
+        <v>0.1288242027312643</v>
       </c>
       <c r="C83">
-        <v>-89.07367304879267</v>
+        <v>-95.29934232016319</v>
       </c>
       <c r="D83">
-        <v>189.9743269512073</v>
+        <v>188.0566576798367</v>
       </c>
       <c r="E83">
-        <v>266.048</v>
+        <v>270.356</v>
       </c>
       <c r="F83">
-        <v>348.948</v>
+        <v>353.256</v>
       </c>
       <c r="G83">
         <v>69.90000000000001</v>
@@ -8221,37 +8221,37 @@
         <v>44.2</v>
       </c>
       <c r="M83">
-        <v>51.22556640000001</v>
+        <v>51.8579808</v>
       </c>
       <c r="N83">
-        <v>-7.025566400000002</v>
+        <v>-7.657980799999997</v>
       </c>
       <c r="O83">
-        <v>-2.107669920000001</v>
+        <v>-2.297394239999999</v>
       </c>
       <c r="P83">
-        <v>-4.917896480000001</v>
+        <v>-5.360586559999998</v>
       </c>
       <c r="Q83">
-        <v>20.58210352</v>
+        <v>20.13941344</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2088744580050416</v>
+        <v>0.2179341501164328</v>
       </c>
       <c r="T83">
-        <v>3.766153764550614</v>
+        <v>3.975384529247871</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2588551173150132</v>
+        <v>0.2556983475916594</v>
       </c>
       <c r="W83">
-        <v>0.1088000687781561</v>
+        <v>0.1092634825735444</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.862850391050044</v>
+        <v>0.8523278253055314</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1288242027312643</v>
+        <v>0.1298342027312643</v>
       </c>
       <c r="C84">
-        <v>-95.29934232016319</v>
+        <v>-101.4866832036202</v>
       </c>
       <c r="D84">
-        <v>188.0566576798367</v>
+        <v>186.1773167963798</v>
       </c>
       <c r="E84">
-        <v>270.356</v>
+        <v>274.664</v>
       </c>
       <c r="F84">
-        <v>353.256</v>
+        <v>357.564</v>
       </c>
       <c r="G84">
         <v>69.90000000000001</v>
@@ -8303,37 +8303,37 @@
         <v>44.2</v>
       </c>
       <c r="M84">
-        <v>51.8579808</v>
+        <v>52.4903952</v>
       </c>
       <c r="N84">
-        <v>-7.657980799999997</v>
+        <v>-8.290395199999999</v>
       </c>
       <c r="O84">
-        <v>-2.297394239999999</v>
+        <v>-2.487118559999999</v>
       </c>
       <c r="P84">
-        <v>-5.360586559999998</v>
+        <v>-5.80327664</v>
       </c>
       <c r="Q84">
-        <v>20.13941344</v>
+        <v>19.69672336</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2179341501164328</v>
+        <v>0.2280596883585759</v>
       </c>
       <c r="T84">
-        <v>3.975384529247871</v>
+        <v>4.209230678027157</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2556983475916594</v>
+        <v>0.2526176446086273</v>
       </c>
       <c r="W84">
-        <v>0.1092634825735444</v>
+        <v>0.1097157297714535</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8523278253055314</v>
+        <v>0.8420588153620913</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1298342027312643</v>
+        <v>0.1308442027312643</v>
       </c>
       <c r="C85">
-        <v>-101.4866832036202</v>
+        <v>-107.636833431457</v>
       </c>
       <c r="D85">
-        <v>186.1773167963798</v>
+        <v>184.335166568543</v>
       </c>
       <c r="E85">
-        <v>274.664</v>
+        <v>278.972</v>
       </c>
       <c r="F85">
-        <v>357.564</v>
+        <v>361.872</v>
       </c>
       <c r="G85">
         <v>69.90000000000001</v>
@@ -8385,37 +8385,37 @@
         <v>44.2</v>
       </c>
       <c r="M85">
-        <v>52.4903952</v>
+        <v>53.1228096</v>
       </c>
       <c r="N85">
-        <v>-8.290395199999999</v>
+        <v>-8.922809600000001</v>
       </c>
       <c r="O85">
-        <v>-2.487118559999999</v>
+        <v>-2.67684288</v>
       </c>
       <c r="P85">
-        <v>-5.80327664</v>
+        <v>-6.24596672</v>
       </c>
       <c r="Q85">
-        <v>19.69672336</v>
+        <v>19.25403328</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2280596883585759</v>
+        <v>0.239450918880987</v>
       </c>
       <c r="T85">
-        <v>4.209230678027157</v>
+        <v>4.472307595403856</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2526176446086273</v>
+        <v>0.2496102916966199</v>
       </c>
       <c r="W85">
-        <v>0.1097157297714535</v>
+        <v>0.1101572091789362</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8420588153620913</v>
+        <v>0.8320343056553997</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1308442027312643</v>
+        <v>0.1318542027312643</v>
       </c>
       <c r="C86">
-        <v>-107.6368334314569</v>
+        <v>-113.750886147524</v>
       </c>
       <c r="D86">
-        <v>184.335166568543</v>
+        <v>182.529113852476</v>
       </c>
       <c r="E86">
-        <v>278.972</v>
+        <v>283.28</v>
       </c>
       <c r="F86">
-        <v>361.872</v>
+        <v>366.1799999999999</v>
       </c>
       <c r="G86">
         <v>69.90000000000001</v>
@@ -8467,37 +8467,37 @@
         <v>44.2</v>
       </c>
       <c r="M86">
-        <v>53.1228096</v>
+        <v>53.755224</v>
       </c>
       <c r="N86">
-        <v>-8.922809599999994</v>
+        <v>-9.555223999999995</v>
       </c>
       <c r="O86">
-        <v>-2.676842879999998</v>
+        <v>-2.866567199999999</v>
       </c>
       <c r="P86">
-        <v>-6.245966719999996</v>
+        <v>-6.688656799999997</v>
       </c>
       <c r="Q86">
-        <v>19.25403328000001</v>
+        <v>18.8113432</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2394509188809868</v>
+        <v>0.2523609801397192</v>
       </c>
       <c r="T86">
-        <v>4.472307595403852</v>
+        <v>4.770461435097443</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2496102916966199</v>
+        <v>0.2466737000296008</v>
       </c>
       <c r="W86">
-        <v>0.1101572091789362</v>
+        <v>0.1105883008356546</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8320343056553998</v>
+        <v>0.8222456667653362</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1318542027312643</v>
+        <v>0.1328642027312643</v>
       </c>
       <c r="C87">
-        <v>-113.750886147524</v>
+        <v>-119.8298920703471</v>
       </c>
       <c r="D87">
-        <v>182.529113852476</v>
+        <v>180.7581079296528</v>
       </c>
       <c r="E87">
-        <v>283.28</v>
+        <v>287.588</v>
       </c>
       <c r="F87">
-        <v>366.1799999999999</v>
+        <v>370.4879999999999</v>
       </c>
       <c r="G87">
         <v>69.90000000000001</v>
@@ -8549,37 +8549,37 @@
         <v>44.2</v>
       </c>
       <c r="M87">
-        <v>53.755224</v>
+        <v>54.3876384</v>
       </c>
       <c r="N87">
-        <v>-9.555223999999995</v>
+        <v>-10.1876384</v>
       </c>
       <c r="O87">
-        <v>-2.866567199999999</v>
+        <v>-3.056291519999999</v>
       </c>
       <c r="P87">
-        <v>-6.688656799999997</v>
+        <v>-7.131346879999999</v>
       </c>
       <c r="Q87">
-        <v>18.8113432</v>
+        <v>18.36865312</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2523609801397192</v>
+        <v>0.2671153358639849</v>
       </c>
       <c r="T87">
-        <v>4.770461435097443</v>
+        <v>5.111208680461545</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2466737000296008</v>
+        <v>0.2438054011920474</v>
       </c>
       <c r="W87">
-        <v>0.1105883008356546</v>
+        <v>0.1110093671050074</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8222456667653362</v>
+        <v>0.8126846706401578</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1328642027312643</v>
+        <v>0.1338742027312643</v>
       </c>
       <c r="C88">
-        <v>-119.8298920703471</v>
+        <v>-125.8748615315284</v>
       </c>
       <c r="D88">
-        <v>180.7581079296528</v>
+        <v>179.0211384684716</v>
       </c>
       <c r="E88">
-        <v>287.588</v>
+        <v>291.896</v>
       </c>
       <c r="F88">
-        <v>370.4879999999999</v>
+        <v>374.7959999999999</v>
       </c>
       <c r="G88">
         <v>69.90000000000001</v>
@@ -8631,37 +8631,37 @@
         <v>44.2</v>
       </c>
       <c r="M88">
-        <v>54.3876384</v>
+        <v>55.02005279999999</v>
       </c>
       <c r="N88">
-        <v>-10.1876384</v>
+        <v>-10.82005279999999</v>
       </c>
       <c r="O88">
-        <v>-3.056291519999999</v>
+        <v>-3.246015839999997</v>
       </c>
       <c r="P88">
-        <v>-7.131346879999999</v>
+        <v>-7.574036959999995</v>
       </c>
       <c r="Q88">
-        <v>18.36865312</v>
+        <v>17.92596304000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2671153358639849</v>
+        <v>0.2841395924689069</v>
       </c>
       <c r="T88">
-        <v>5.111208680461545</v>
+        <v>5.504378578958589</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2438054011920474</v>
+        <v>0.2410030402588054</v>
       </c>
       <c r="W88">
-        <v>0.1110093671050074</v>
+        <v>0.1114207536900074</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8126846706401578</v>
+        <v>0.8033434675293516</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1338742027312643</v>
+        <v>0.1846147731588404</v>
       </c>
       <c r="C89">
-        <v>-125.8748615315284</v>
+        <v>-188.4686624222972</v>
       </c>
       <c r="D89">
-        <v>179.0211384684716</v>
+        <v>120.7353375777028</v>
       </c>
       <c r="E89">
-        <v>291.896</v>
+        <v>296.204</v>
       </c>
       <c r="F89">
-        <v>374.7959999999999</v>
+        <v>379.104</v>
       </c>
       <c r="G89">
         <v>69.90000000000001</v>
@@ -8713,45 +8713,45 @@
         <v>44.2</v>
       </c>
       <c r="M89">
-        <v>55.02005279999999</v>
+        <v>76.1240832</v>
       </c>
       <c r="N89">
-        <v>-10.82005279999999</v>
+        <v>-31.9240832</v>
       </c>
       <c r="O89">
-        <v>-3.246015839999997</v>
+        <v>-9.577224959999999</v>
       </c>
       <c r="P89">
-        <v>-7.574036959999995</v>
+        <v>-22.34685824</v>
       </c>
       <c r="Q89">
-        <v>17.92596304000001</v>
+        <v>3.15314176</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2841395924689069</v>
+        <v>0.3224226454044496</v>
       </c>
       <c r="T89">
-        <v>5.504378578958589</v>
+        <v>6.388513750680129</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.2410030402588054</v>
+        <v>0.1741892899407687</v>
       </c>
       <c r="W89">
-        <v>0.1114207536900074</v>
+        <v>0.1658227905798937</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8033434675293516</v>
+        <v>0.5806309664692291</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1846147731588404</v>
+        <v>0.1861647731588403</v>
       </c>
       <c r="C90">
-        <v>-188.4686624222972</v>
+        <v>-193.9656332207354</v>
       </c>
       <c r="D90">
-        <v>120.7353375777028</v>
+        <v>119.5463667792646</v>
       </c>
       <c r="E90">
-        <v>296.204</v>
+        <v>300.5119999999999</v>
       </c>
       <c r="F90">
-        <v>379.104</v>
+        <v>383.412</v>
       </c>
       <c r="G90">
         <v>69.90000000000001</v>
@@ -8795,37 +8795,37 @@
         <v>44.2</v>
       </c>
       <c r="M90">
-        <v>76.1240832</v>
+        <v>76.9891296</v>
       </c>
       <c r="N90">
-        <v>-31.9240832</v>
+        <v>-32.7891296</v>
       </c>
       <c r="O90">
-        <v>-9.577224959999999</v>
+        <v>-9.836738879999999</v>
       </c>
       <c r="P90">
-        <v>-22.34685824</v>
+        <v>-22.95239072</v>
       </c>
       <c r="Q90">
-        <v>3.15314176</v>
+        <v>2.547609280000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3224226454044496</v>
+        <v>0.3475701586230359</v>
       </c>
       <c r="T90">
-        <v>6.388513750680129</v>
+        <v>6.969287728014686</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1741892899407687</v>
+        <v>0.1722321069077264</v>
       </c>
       <c r="W90">
-        <v>0.1658227905798937</v>
+        <v>0.1662157929329285</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5806309664692291</v>
+        <v>0.5741070230257546</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1861647731588403</v>
+        <v>0.1877147731588404</v>
       </c>
       <c r="C91">
-        <v>-193.9656332207354</v>
+        <v>-199.4394150164494</v>
       </c>
       <c r="D91">
-        <v>119.5463667792646</v>
+        <v>118.3805849835506</v>
       </c>
       <c r="E91">
-        <v>300.5119999999999</v>
+        <v>304.8199999999999</v>
       </c>
       <c r="F91">
-        <v>383.412</v>
+        <v>387.72</v>
       </c>
       <c r="G91">
         <v>69.90000000000001</v>
@@ -8877,37 +8877,37 @@
         <v>44.2</v>
       </c>
       <c r="M91">
-        <v>76.9891296</v>
+        <v>77.854176</v>
       </c>
       <c r="N91">
-        <v>-32.7891296</v>
+        <v>-33.65417599999999</v>
       </c>
       <c r="O91">
-        <v>-9.836738879999999</v>
+        <v>-10.0962528</v>
       </c>
       <c r="P91">
-        <v>-22.95239072</v>
+        <v>-23.5579232</v>
       </c>
       <c r="Q91">
-        <v>2.547609280000003</v>
+        <v>1.942076800000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3475701586230359</v>
+        <v>0.3777471744853396</v>
       </c>
       <c r="T91">
-        <v>6.969287728014686</v>
+        <v>7.666216500816156</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1722321069077264</v>
+        <v>0.1703184168309738</v>
       </c>
       <c r="W91">
-        <v>0.1662157929329285</v>
+        <v>0.1666000619003405</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5741070230257546</v>
+        <v>0.5677280561032463</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1877147731588404</v>
+        <v>0.1892647731588404</v>
       </c>
       <c r="C92">
-        <v>-199.4394150164494</v>
+        <v>-204.8906796552532</v>
       </c>
       <c r="D92">
-        <v>118.3805849835506</v>
+        <v>117.2373203447468</v>
       </c>
       <c r="E92">
-        <v>304.8199999999999</v>
+        <v>309.1279999999999</v>
       </c>
       <c r="F92">
-        <v>387.72</v>
+        <v>392.028</v>
       </c>
       <c r="G92">
         <v>69.90000000000001</v>
@@ -8959,37 +8959,37 @@
         <v>44.2</v>
       </c>
       <c r="M92">
-        <v>77.854176</v>
+        <v>78.71922239999999</v>
       </c>
       <c r="N92">
-        <v>-33.65417599999999</v>
+        <v>-34.51922239999999</v>
       </c>
       <c r="O92">
-        <v>-10.0962528</v>
+        <v>-10.35576672</v>
       </c>
       <c r="P92">
-        <v>-23.5579232</v>
+        <v>-24.16345567999999</v>
       </c>
       <c r="Q92">
-        <v>1.942076800000002</v>
+        <v>1.336544320000009</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3777471744853396</v>
+        <v>0.4146301938725996</v>
       </c>
       <c r="T92">
-        <v>7.666216500816156</v>
+        <v>8.518018334240175</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1703184168309738</v>
+        <v>0.1684467858767874</v>
       </c>
       <c r="W92">
-        <v>0.1666000619003405</v>
+        <v>0.1669758853959411</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5677280561032463</v>
+        <v>0.5614892862559578</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1892647731588404</v>
+        <v>0.1908147731588404</v>
       </c>
       <c r="C93">
-        <v>-204.8906796552532</v>
+        <v>-210.3200732777121</v>
       </c>
       <c r="D93">
-        <v>117.2373203447468</v>
+        <v>116.1159267222878</v>
       </c>
       <c r="E93">
-        <v>309.1279999999999</v>
+        <v>313.4359999999999</v>
       </c>
       <c r="F93">
-        <v>392.028</v>
+        <v>396.336</v>
       </c>
       <c r="G93">
         <v>69.90000000000001</v>
@@ -9041,37 +9041,37 @@
         <v>44.2</v>
       </c>
       <c r="M93">
-        <v>78.71922239999999</v>
+        <v>79.58426879999999</v>
       </c>
       <c r="N93">
-        <v>-34.51922239999999</v>
+        <v>-35.38426879999999</v>
       </c>
       <c r="O93">
-        <v>-10.35576672</v>
+        <v>-10.61528064</v>
       </c>
       <c r="P93">
-        <v>-24.16345567999999</v>
+        <v>-24.76898815999999</v>
       </c>
       <c r="Q93">
-        <v>1.336544320000009</v>
+        <v>0.7310118400000079</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4146301938725996</v>
+        <v>0.4607339681066746</v>
       </c>
       <c r="T93">
-        <v>8.518018334240175</v>
+        <v>9.582770626020199</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1684467858767874</v>
+        <v>0.1666158425520397</v>
       </c>
       <c r="W93">
-        <v>0.1669758853959411</v>
+        <v>0.1673435388155504</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5614892862559578</v>
+        <v>0.5553861418401322</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1908147731588404</v>
+        <v>0.1923647731588403</v>
       </c>
       <c r="C94">
-        <v>-210.3200732777121</v>
+        <v>-215.7282175368697</v>
       </c>
       <c r="D94">
-        <v>116.1159267222878</v>
+        <v>115.0157824631303</v>
       </c>
       <c r="E94">
-        <v>313.4359999999999</v>
+        <v>317.744</v>
       </c>
       <c r="F94">
-        <v>396.336</v>
+        <v>400.644</v>
       </c>
       <c r="G94">
         <v>69.90000000000001</v>
@@ -9123,37 +9123,37 @@
         <v>44.2</v>
       </c>
       <c r="M94">
-        <v>79.58426879999999</v>
+        <v>80.4493152</v>
       </c>
       <c r="N94">
-        <v>-35.38426879999999</v>
+        <v>-36.2493152</v>
       </c>
       <c r="O94">
-        <v>-10.61528064</v>
+        <v>-10.87479456</v>
       </c>
       <c r="P94">
-        <v>-24.76898815999999</v>
+        <v>-25.37452064</v>
       </c>
       <c r="Q94">
-        <v>0.7310118400000079</v>
+        <v>0.1254793599999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4607339681066746</v>
+        <v>0.5200102492647709</v>
       </c>
       <c r="T94">
-        <v>9.582770626020199</v>
+        <v>10.9517378583088</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1666158425520397</v>
+        <v>0.1648242743525553</v>
       </c>
       <c r="W94">
-        <v>0.1673435388155504</v>
+        <v>0.1677032857100069</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5553861418401322</v>
+        <v>0.5494142478418511</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1923647731588403</v>
+        <v>0.1939147731588404</v>
       </c>
       <c r="C95">
-        <v>-215.7282175368697</v>
+        <v>-221.1157107473985</v>
       </c>
       <c r="D95">
-        <v>115.0157824631303</v>
+        <v>113.9362892526015</v>
       </c>
       <c r="E95">
-        <v>317.744</v>
+        <v>322.052</v>
       </c>
       <c r="F95">
-        <v>400.644</v>
+        <v>404.952</v>
       </c>
       <c r="G95">
         <v>69.90000000000001</v>
@@ -9205,37 +9205,37 @@
         <v>44.2</v>
       </c>
       <c r="M95">
-        <v>80.4493152</v>
+        <v>81.3143616</v>
       </c>
       <c r="N95">
-        <v>-36.2493152</v>
+        <v>-37.1143616</v>
       </c>
       <c r="O95">
-        <v>-10.87479456</v>
+        <v>-11.13430848</v>
       </c>
       <c r="P95">
-        <v>-25.37452064</v>
+        <v>-25.98005312</v>
       </c>
       <c r="Q95">
-        <v>0.1254793599999999</v>
+        <v>-0.4800531199999973</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5200102492647709</v>
+        <v>0.5990452908088996</v>
       </c>
       <c r="T95">
-        <v>10.9517378583088</v>
+        <v>12.77702750136027</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1648242743525553</v>
+        <v>0.1630708246254005</v>
       </c>
       <c r="W95">
-        <v>0.1677032857100069</v>
+        <v>0.1680553784152196</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5494142478418511</v>
+        <v>0.5435694154180017</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1939147731588404</v>
+        <v>0.1954647731588404</v>
       </c>
       <c r="C96">
-        <v>-221.1157107473985</v>
+        <v>-226.4831289706408</v>
       </c>
       <c r="D96">
-        <v>113.9362892526015</v>
+        <v>112.8768710293592</v>
       </c>
       <c r="E96">
-        <v>322.052</v>
+        <v>326.36</v>
       </c>
       <c r="F96">
-        <v>404.952</v>
+        <v>409.26</v>
       </c>
       <c r="G96">
         <v>69.90000000000001</v>
@@ -9287,37 +9287,37 @@
         <v>44.2</v>
       </c>
       <c r="M96">
-        <v>81.3143616</v>
+        <v>82.179408</v>
       </c>
       <c r="N96">
-        <v>-37.1143616</v>
+        <v>-37.97940799999999</v>
       </c>
       <c r="O96">
-        <v>-11.13430848</v>
+        <v>-11.3938224</v>
       </c>
       <c r="P96">
-        <v>-25.98005312</v>
+        <v>-26.58558559999999</v>
       </c>
       <c r="Q96">
-        <v>-0.4800531199999973</v>
+        <v>-1.085585599999995</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5990452908088996</v>
+        <v>0.7096943489706798</v>
       </c>
       <c r="T96">
-        <v>12.77702750136027</v>
+        <v>15.33243300163233</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1630708246254005</v>
+        <v>0.1613542896293436</v>
       </c>
       <c r="W96">
-        <v>0.1680553784152196</v>
+        <v>0.1684000586424278</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5435694154180017</v>
+        <v>0.5378476320978123</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1954647731588404</v>
+        <v>0.1970147731588404</v>
       </c>
       <c r="C97">
-        <v>-226.4831289706408</v>
+        <v>-231.8310270396727</v>
       </c>
       <c r="D97">
-        <v>112.8768710293592</v>
+        <v>111.8369729603273</v>
       </c>
       <c r="E97">
-        <v>326.36</v>
+        <v>330.668</v>
       </c>
       <c r="F97">
-        <v>409.26</v>
+        <v>413.568</v>
       </c>
       <c r="G97">
         <v>69.90000000000001</v>
@@ -9369,37 +9369,37 @@
         <v>44.2</v>
       </c>
       <c r="M97">
-        <v>82.179408</v>
+        <v>83.04445439999999</v>
       </c>
       <c r="N97">
-        <v>-37.97940799999999</v>
+        <v>-38.84445439999999</v>
       </c>
       <c r="O97">
-        <v>-11.3938224</v>
+        <v>-11.65333632</v>
       </c>
       <c r="P97">
-        <v>-26.58558559999999</v>
+        <v>-27.19111808</v>
       </c>
       <c r="Q97">
-        <v>-1.085585599999995</v>
+        <v>-1.691118079999995</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7096943489706798</v>
+        <v>0.87566793621335</v>
       </c>
       <c r="T97">
-        <v>15.33243300163233</v>
+        <v>19.16554125204042</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1613542896293436</v>
+        <v>0.159673515779038</v>
       </c>
       <c r="W97">
-        <v>0.1684000586424278</v>
+        <v>0.1687375580315692</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5378476320978123</v>
+        <v>0.5322450525967933</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1970147731588403</v>
+        <v>0.1985647731588404</v>
       </c>
       <c r="C98">
-        <v>-231.8310270396726</v>
+        <v>-237.1599395282226</v>
       </c>
       <c r="D98">
-        <v>111.8369729603273</v>
+        <v>110.8160604717773</v>
       </c>
       <c r="E98">
-        <v>330.6679999999999</v>
+        <v>334.9759999999999</v>
       </c>
       <c r="F98">
-        <v>413.5679999999999</v>
+        <v>417.8759999999999</v>
       </c>
       <c r="G98">
         <v>69.90000000000001</v>
@@ -9451,37 +9451,37 @@
         <v>44.2</v>
       </c>
       <c r="M98">
-        <v>83.04445439999999</v>
+        <v>83.90950079999999</v>
       </c>
       <c r="N98">
-        <v>-38.84445439999999</v>
+        <v>-39.70950079999999</v>
       </c>
       <c r="O98">
-        <v>-11.65333632</v>
+        <v>-11.91285024</v>
       </c>
       <c r="P98">
-        <v>-27.19111808</v>
+        <v>-27.79665055999999</v>
       </c>
       <c r="Q98">
-        <v>-1.691118079999995</v>
+        <v>-2.296650559999989</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8756679362133479</v>
+        <v>1.152290581617797</v>
       </c>
       <c r="T98">
-        <v>19.16554125204037</v>
+        <v>25.55405500272049</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.159673515779038</v>
+        <v>0.1580273970596665</v>
       </c>
       <c r="W98">
-        <v>0.1687375580315692</v>
+        <v>0.169068098670419</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5322450525967933</v>
+        <v>0.5267579901988884</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1985647731588404</v>
+        <v>0.2001147731588404</v>
       </c>
       <c r="C99">
-        <v>-237.1599395282226</v>
+        <v>-242.4703816670025</v>
       </c>
       <c r="D99">
-        <v>110.8160604717773</v>
+        <v>109.8136183329974</v>
       </c>
       <c r="E99">
-        <v>334.9759999999999</v>
+        <v>339.284</v>
       </c>
       <c r="F99">
-        <v>417.8759999999999</v>
+        <v>422.184</v>
       </c>
       <c r="G99">
         <v>69.90000000000001</v>
@@ -9533,37 +9533,37 @@
         <v>44.2</v>
       </c>
       <c r="M99">
-        <v>83.90950079999999</v>
+        <v>84.7745472</v>
       </c>
       <c r="N99">
-        <v>-39.70950079999999</v>
+        <v>-40.5745472</v>
       </c>
       <c r="O99">
-        <v>-11.91285024</v>
+        <v>-12.17236416</v>
       </c>
       <c r="P99">
-        <v>-27.79665055999999</v>
+        <v>-28.40218304</v>
       </c>
       <c r="Q99">
-        <v>-2.296650559999989</v>
+        <v>-2.902183039999997</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.152290581617797</v>
+        <v>1.705535872426696</v>
       </c>
       <c r="T99">
-        <v>25.55405500272049</v>
+        <v>38.33108250408074</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1580273970596665</v>
+        <v>0.1564148725998739</v>
       </c>
       <c r="W99">
-        <v>0.169068098670419</v>
+        <v>0.1693918935819453</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5267579901988884</v>
+        <v>0.5213829086662465</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2001147731588404</v>
+        <v>0.2016647731588404</v>
       </c>
       <c r="C100">
-        <v>-242.4703816670025</v>
+        <v>-247.7628502107487</v>
       </c>
       <c r="D100">
-        <v>109.8136183329974</v>
+        <v>108.8291497892513</v>
       </c>
       <c r="E100">
-        <v>339.284</v>
+        <v>343.592</v>
       </c>
       <c r="F100">
-        <v>422.184</v>
+        <v>426.492</v>
       </c>
       <c r="G100">
         <v>69.90000000000001</v>
@@ -9615,37 +9615,37 @@
         <v>44.2</v>
       </c>
       <c r="M100">
-        <v>84.7745472</v>
+        <v>85.6395936</v>
       </c>
       <c r="N100">
-        <v>-40.5745472</v>
+        <v>-41.43959359999999</v>
       </c>
       <c r="O100">
-        <v>-12.17236416</v>
+        <v>-12.43187808</v>
       </c>
       <c r="P100">
-        <v>-28.40218304</v>
+        <v>-29.00771552</v>
       </c>
       <c r="Q100">
-        <v>-2.902183039999997</v>
+        <v>-3.507715519999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.705535872426696</v>
+        <v>3.365271744853392</v>
       </c>
       <c r="T100">
-        <v>38.33108250408074</v>
+        <v>76.66216500816149</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1564148725998739</v>
+        <v>0.1548349243917944</v>
       </c>
       <c r="W100">
-        <v>0.1693918935819453</v>
+        <v>0.1697091471821277</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5213829086662465</v>
+        <v>0.5161164146393147</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2016647731588404</v>
-      </c>
-      <c r="C101">
-        <v>-247.7628502107487</v>
-      </c>
-      <c r="D101">
-        <v>108.8291497892513</v>
-      </c>
-      <c r="E101">
-        <v>343.592</v>
-      </c>
-      <c r="F101">
-        <v>426.492</v>
-      </c>
-      <c r="G101">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="H101">
-        <v>347.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>69.7</v>
-      </c>
-      <c r="K101">
-        <v>25.5</v>
-      </c>
-      <c r="L101">
-        <v>44.2</v>
-      </c>
-      <c r="M101">
-        <v>85.6395936</v>
-      </c>
-      <c r="N101">
-        <v>-41.43959359999999</v>
-      </c>
-      <c r="O101">
-        <v>-12.43187808</v>
-      </c>
-      <c r="P101">
-        <v>-29.00771552</v>
-      </c>
-      <c r="Q101">
-        <v>-3.507715519999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.365271744853392</v>
-      </c>
-      <c r="T101">
-        <v>76.66216500816149</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1548349243917944</v>
-      </c>
-      <c r="W101">
-        <v>0.1697091471821277</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5161164146393147</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
